--- a/Data/Corse2025-IA-FGA+EM/Corse2025_InfosProtocole.xlsx
+++ b/Data/Corse2025-IA-FGA+EM/Corse2025_InfosProtocole.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Data Activité Béliers" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Data Détecteur IA" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="All Data EM ODARC 2025" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Sheet7" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="IA" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId10"/>
@@ -1836,42 +1836,8 @@
 </comments>
 </file>
 
-<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A51" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Nathalie DEBUS:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Eponge perdue</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="251">
   <si>
     <t xml:space="preserve">Programme cadre CNE: FGA et Effet mâle - ODARC (Altiani, Corse) - 2025</t>
   </si>
@@ -4432,10 +4398,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0739626647792621"/>
-          <c:y val="0.0798226164079823"/>
-          <c:w val="0.899761125364947"/>
-          <c:h val="0.766792748141385"/>
+          <c:x val="0.0739692089895594"/>
+          <c:y val="0.0798330289590399"/>
+          <c:w val="0.899663776322775"/>
+          <c:h val="0.766631881033133"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -4690,11 +4656,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="64567175"/>
-        <c:axId val="95246886"/>
+        <c:axId val="71951626"/>
+        <c:axId val="43969253"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="64567175"/>
+        <c:axId val="71951626"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="45801.458333333"/>
@@ -4728,13 +4694,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95246886"/>
+        <c:crossAx val="43969253"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="95246886"/>
+        <c:axId val="43969253"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4810,7 +4776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64567175"/>
+        <c:crossAx val="71951626"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4907,8 +4873,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.247919018058691"/>
-          <c:y val="0.0117788085683015"/>
+          <c:x val="0.248007054673721"/>
+          <c:y val="0.0117279124315872"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -4926,10 +4892,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0504726297968397"/>
-          <c:y val="0.0611351435868036"/>
-          <c:w val="0.88551072234763"/>
-          <c:h val="0.803564913743681"/>
+          <c:x val="0.0504761904761905"/>
+          <c:y val="0.0611415168100078"/>
+          <c:w val="0.885432098765432"/>
+          <c:h val="0.803440187646599"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -6935,11 +6901,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="36685644"/>
-        <c:axId val="24051171"/>
+        <c:axId val="82793315"/>
+        <c:axId val="39023013"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="36685644"/>
+        <c:axId val="82793315"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="45801.62599999"/>
@@ -6977,8 +6943,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.949844808126411"/>
-              <c:y val="0.937092823265753"/>
+              <c:x val="0.949770723104056"/>
+              <c:y val="0.937086265311441"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -7016,14 +6982,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24051171"/>
+        <c:crossAx val="39023013"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.0833333333"/>
         <c:minorUnit val="0.04166666665"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="24051171"/>
+        <c:axId val="39023013"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="50"/>
@@ -7081,8 +7047,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.0065956546275395"/>
-              <c:y val="0.388387971022046"/>
+              <c:x val="0.00659611992945326"/>
+              <c:y val="0.388219963513161"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -7119,7 +7085,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36685644"/>
+        <c:crossAx val="82793315"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="2"/>
@@ -7162,9 +7128,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>612720</xdr:colOff>
+      <xdr:colOff>612000</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>103320</xdr:rowOff>
+      <xdr:rowOff>102600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7173,7 +7139,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9758520" y="542880"/>
-        <a:ext cx="8137800" cy="5519880"/>
+        <a:ext cx="8137080" cy="5519160"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7197,9 +7163,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>75600</xdr:colOff>
+      <xdr:colOff>74880</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>116280</xdr:rowOff>
+      <xdr:rowOff>115560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7208,7 +7174,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="10718280" y="596160"/>
-        <a:ext cx="10206360" cy="6906960"/>
+        <a:ext cx="10205640" cy="6906240"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7814,51 +7780,51 @@
     </row>
     <row r="23" s="7" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
-      <c r="B23" s="0"/>
+      <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="0"/>
-      <c r="F23" s="0"/>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
-      <c r="I23" s="0"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
     </row>
     <row r="24" s="7" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="0"/>
+      <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="0"/>
-      <c r="F24" s="0"/>
-      <c r="G24" s="0"/>
-      <c r="H24" s="0"/>
-      <c r="I24" s="0"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
     </row>
     <row r="25" s="7" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1"/>
-      <c r="B25" s="0"/>
+      <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="0"/>
-      <c r="F25" s="0"/>
-      <c r="G25" s="0"/>
-      <c r="H25" s="0"/>
-      <c r="I25" s="0"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
     </row>
     <row r="26" s="7" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="0"/>
+      <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="0"/>
-      <c r="F26" s="0"/>
-      <c r="G26" s="0"/>
-      <c r="H26" s="0"/>
-      <c r="I26" s="0"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
     </row>
     <row r="27" s="7" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
@@ -12871,7 +12837,7 @@
       </c>
       <c r="E55" s="41"/>
     </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" s="34" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="36"/>
       <c r="B56" s="35" t="n">
         <f aca="false">B55+1</f>
@@ -12884,6 +12850,238 @@
         <v>28</v>
       </c>
       <c r="E56" s="37"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+      <c r="M56" s="7"/>
+      <c r="N56" s="7"/>
+      <c r="O56" s="7"/>
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
+      <c r="R56" s="7"/>
+      <c r="S56" s="7"/>
+      <c r="T56" s="7"/>
+      <c r="U56" s="7"/>
+      <c r="V56" s="7"/>
+      <c r="W56" s="7"/>
+      <c r="X56" s="7"/>
+      <c r="Y56" s="7"/>
+      <c r="Z56" s="7"/>
+      <c r="AA56" s="7"/>
+      <c r="AB56" s="7"/>
+      <c r="AC56" s="7"/>
+      <c r="AD56" s="7"/>
+      <c r="AE56" s="7"/>
+      <c r="AF56" s="7"/>
+      <c r="AG56" s="7"/>
+      <c r="AH56" s="7"/>
+      <c r="AI56" s="7"/>
+      <c r="AJ56" s="7"/>
+      <c r="AK56" s="7"/>
+      <c r="AL56" s="7"/>
+      <c r="AM56" s="7"/>
+      <c r="AN56" s="7"/>
+      <c r="AO56" s="7"/>
+      <c r="AP56" s="7"/>
+      <c r="AQ56" s="7"/>
+      <c r="AR56" s="7"/>
+      <c r="AS56" s="7"/>
+      <c r="AT56" s="7"/>
+      <c r="AU56" s="7"/>
+      <c r="AV56" s="7"/>
+      <c r="AW56" s="7"/>
+      <c r="AX56" s="7"/>
+      <c r="AY56" s="7"/>
+      <c r="AZ56" s="7"/>
+      <c r="BA56" s="7"/>
+      <c r="BB56" s="7"/>
+      <c r="BC56" s="7"/>
+      <c r="BD56" s="7"/>
+      <c r="BE56" s="7"/>
+      <c r="BF56" s="7"/>
+      <c r="BG56" s="7"/>
+      <c r="BH56" s="7"/>
+      <c r="BI56" s="7"/>
+      <c r="BJ56" s="7"/>
+      <c r="BK56" s="7"/>
+      <c r="BL56" s="7"/>
+      <c r="BM56" s="7"/>
+      <c r="BN56" s="7"/>
+      <c r="BO56" s="7"/>
+      <c r="BP56" s="7"/>
+      <c r="BQ56" s="7"/>
+      <c r="BR56" s="7"/>
+      <c r="BS56" s="7"/>
+      <c r="BT56" s="7"/>
+      <c r="BU56" s="7"/>
+      <c r="BV56" s="7"/>
+      <c r="BW56" s="7"/>
+      <c r="BX56" s="7"/>
+      <c r="BY56" s="7"/>
+      <c r="BZ56" s="7"/>
+      <c r="CA56" s="7"/>
+      <c r="CB56" s="7"/>
+      <c r="CC56" s="7"/>
+      <c r="CD56" s="7"/>
+      <c r="CE56" s="7"/>
+      <c r="CF56" s="7"/>
+      <c r="CG56" s="7"/>
+      <c r="CH56" s="7"/>
+      <c r="CI56" s="7"/>
+      <c r="CJ56" s="7"/>
+      <c r="CK56" s="7"/>
+      <c r="CL56" s="7"/>
+      <c r="CM56" s="7"/>
+      <c r="CN56" s="7"/>
+      <c r="CO56" s="7"/>
+      <c r="CP56" s="7"/>
+      <c r="CQ56" s="7"/>
+      <c r="CR56" s="7"/>
+      <c r="CS56" s="7"/>
+      <c r="CT56" s="7"/>
+      <c r="CU56" s="7"/>
+      <c r="CV56" s="7"/>
+      <c r="CW56" s="7"/>
+      <c r="CX56" s="7"/>
+      <c r="CY56" s="7"/>
+      <c r="CZ56" s="7"/>
+      <c r="DA56" s="7"/>
+      <c r="DB56" s="7"/>
+      <c r="DC56" s="7"/>
+      <c r="DD56" s="7"/>
+      <c r="DE56" s="7"/>
+      <c r="DF56" s="7"/>
+      <c r="DG56" s="7"/>
+      <c r="DH56" s="7"/>
+      <c r="DI56" s="7"/>
+      <c r="DJ56" s="7"/>
+      <c r="DK56" s="7"/>
+      <c r="DL56" s="7"/>
+      <c r="DM56" s="7"/>
+      <c r="DN56" s="7"/>
+      <c r="DO56" s="7"/>
+      <c r="DP56" s="7"/>
+      <c r="DQ56" s="7"/>
+      <c r="DR56" s="7"/>
+      <c r="DS56" s="7"/>
+      <c r="DT56" s="7"/>
+      <c r="DU56" s="7"/>
+      <c r="DV56" s="7"/>
+      <c r="DW56" s="7"/>
+      <c r="DX56" s="7"/>
+      <c r="DY56" s="7"/>
+      <c r="DZ56" s="7"/>
+      <c r="EA56" s="7"/>
+      <c r="EB56" s="7"/>
+      <c r="EC56" s="7"/>
+      <c r="ED56" s="7"/>
+      <c r="EE56" s="7"/>
+      <c r="EF56" s="7"/>
+      <c r="EG56" s="7"/>
+      <c r="EH56" s="7"/>
+      <c r="EI56" s="7"/>
+      <c r="EJ56" s="7"/>
+      <c r="EK56" s="7"/>
+      <c r="EL56" s="7"/>
+      <c r="EM56" s="7"/>
+      <c r="EN56" s="7"/>
+      <c r="EO56" s="7"/>
+      <c r="EP56" s="7"/>
+      <c r="EQ56" s="7"/>
+      <c r="ER56" s="7"/>
+      <c r="ES56" s="7"/>
+      <c r="ET56" s="7"/>
+      <c r="EU56" s="7"/>
+      <c r="EV56" s="7"/>
+      <c r="EW56" s="7"/>
+      <c r="EX56" s="7"/>
+      <c r="EY56" s="7"/>
+      <c r="EZ56" s="7"/>
+      <c r="FA56" s="7"/>
+      <c r="FB56" s="7"/>
+      <c r="FC56" s="7"/>
+      <c r="FD56" s="7"/>
+      <c r="FE56" s="7"/>
+      <c r="FF56" s="7"/>
+      <c r="FG56" s="7"/>
+      <c r="FH56" s="7"/>
+      <c r="FI56" s="7"/>
+      <c r="FJ56" s="7"/>
+      <c r="FK56" s="7"/>
+      <c r="FL56" s="7"/>
+      <c r="FM56" s="7"/>
+      <c r="FN56" s="7"/>
+      <c r="FO56" s="7"/>
+      <c r="FP56" s="7"/>
+      <c r="FQ56" s="7"/>
+      <c r="FR56" s="7"/>
+      <c r="FS56" s="7"/>
+      <c r="FT56" s="7"/>
+      <c r="FU56" s="7"/>
+      <c r="FV56" s="7"/>
+      <c r="FW56" s="7"/>
+      <c r="FX56" s="7"/>
+      <c r="FY56" s="7"/>
+      <c r="FZ56" s="7"/>
+      <c r="GA56" s="7"/>
+      <c r="GB56" s="7"/>
+      <c r="GC56" s="7"/>
+      <c r="GD56" s="7"/>
+      <c r="GE56" s="7"/>
+      <c r="GF56" s="7"/>
+      <c r="GG56" s="7"/>
+      <c r="GH56" s="7"/>
+      <c r="GI56" s="7"/>
+      <c r="GJ56" s="7"/>
+      <c r="GK56" s="7"/>
+      <c r="GL56" s="7"/>
+      <c r="GM56" s="7"/>
+      <c r="GN56" s="7"/>
+      <c r="GO56" s="7"/>
+      <c r="GP56" s="7"/>
+      <c r="GQ56" s="7"/>
+      <c r="GR56" s="7"/>
+      <c r="GS56" s="7"/>
+      <c r="GT56" s="7"/>
+      <c r="GU56" s="7"/>
+      <c r="GV56" s="7"/>
+      <c r="GW56" s="7"/>
+      <c r="GX56" s="7"/>
+      <c r="GY56" s="7"/>
+      <c r="GZ56" s="7"/>
+      <c r="HA56" s="7"/>
+      <c r="HB56" s="7"/>
+      <c r="HC56" s="7"/>
+      <c r="HD56" s="7"/>
+      <c r="HE56" s="7"/>
+      <c r="HF56" s="7"/>
+      <c r="HG56" s="7"/>
+      <c r="HH56" s="7"/>
+      <c r="HI56" s="7"/>
+      <c r="HJ56" s="7"/>
+      <c r="HK56" s="7"/>
+      <c r="HL56" s="7"/>
+      <c r="HM56" s="7"/>
+      <c r="HN56" s="7"/>
+      <c r="HO56" s="7"/>
+      <c r="HP56" s="7"/>
+      <c r="HQ56" s="7"/>
+      <c r="HR56" s="7"/>
+      <c r="HS56" s="7"/>
+      <c r="HT56" s="7"/>
+      <c r="HU56" s="7"/>
+      <c r="HV56" s="7"/>
+      <c r="HW56" s="7"/>
+      <c r="HX56" s="7"/>
+      <c r="HY56" s="7"/>
+      <c r="HZ56" s="7"/>
+      <c r="IA56" s="7"/>
+      <c r="IB56" s="7"/>
+      <c r="IC56" s="7"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="36"/>
@@ -12899,7 +13097,7 @@
       </c>
       <c r="E57" s="37"/>
     </row>
-    <row r="58" s="34" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="32"/>
       <c r="B58" s="31" t="n">
         <f aca="false">B57+1</f>
@@ -12912,240 +13110,8 @@
         <v>30</v>
       </c>
       <c r="E58" s="33"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
-      <c r="K58" s="7"/>
-      <c r="L58" s="7"/>
-      <c r="M58" s="7"/>
-      <c r="N58" s="7"/>
-      <c r="O58" s="7"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="7"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="7"/>
-      <c r="T58" s="7"/>
-      <c r="U58" s="7"/>
-      <c r="V58" s="7"/>
-      <c r="W58" s="7"/>
-      <c r="X58" s="7"/>
-      <c r="Y58" s="7"/>
-      <c r="Z58" s="7"/>
-      <c r="AA58" s="7"/>
-      <c r="AB58" s="7"/>
-      <c r="AC58" s="7"/>
-      <c r="AD58" s="7"/>
-      <c r="AE58" s="7"/>
-      <c r="AF58" s="7"/>
-      <c r="AG58" s="7"/>
-      <c r="AH58" s="7"/>
-      <c r="AI58" s="7"/>
-      <c r="AJ58" s="7"/>
-      <c r="AK58" s="7"/>
-      <c r="AL58" s="7"/>
-      <c r="AM58" s="7"/>
-      <c r="AN58" s="7"/>
-      <c r="AO58" s="7"/>
-      <c r="AP58" s="7"/>
-      <c r="AQ58" s="7"/>
-      <c r="AR58" s="7"/>
-      <c r="AS58" s="7"/>
-      <c r="AT58" s="7"/>
-      <c r="AU58" s="7"/>
-      <c r="AV58" s="7"/>
-      <c r="AW58" s="7"/>
-      <c r="AX58" s="7"/>
-      <c r="AY58" s="7"/>
-      <c r="AZ58" s="7"/>
-      <c r="BA58" s="7"/>
-      <c r="BB58" s="7"/>
-      <c r="BC58" s="7"/>
-      <c r="BD58" s="7"/>
-      <c r="BE58" s="7"/>
-      <c r="BF58" s="7"/>
-      <c r="BG58" s="7"/>
-      <c r="BH58" s="7"/>
-      <c r="BI58" s="7"/>
-      <c r="BJ58" s="7"/>
-      <c r="BK58" s="7"/>
-      <c r="BL58" s="7"/>
-      <c r="BM58" s="7"/>
-      <c r="BN58" s="7"/>
-      <c r="BO58" s="7"/>
-      <c r="BP58" s="7"/>
-      <c r="BQ58" s="7"/>
-      <c r="BR58" s="7"/>
-      <c r="BS58" s="7"/>
-      <c r="BT58" s="7"/>
-      <c r="BU58" s="7"/>
-      <c r="BV58" s="7"/>
-      <c r="BW58" s="7"/>
-      <c r="BX58" s="7"/>
-      <c r="BY58" s="7"/>
-      <c r="BZ58" s="7"/>
-      <c r="CA58" s="7"/>
-      <c r="CB58" s="7"/>
-      <c r="CC58" s="7"/>
-      <c r="CD58" s="7"/>
-      <c r="CE58" s="7"/>
-      <c r="CF58" s="7"/>
-      <c r="CG58" s="7"/>
-      <c r="CH58" s="7"/>
-      <c r="CI58" s="7"/>
-      <c r="CJ58" s="7"/>
-      <c r="CK58" s="7"/>
-      <c r="CL58" s="7"/>
-      <c r="CM58" s="7"/>
-      <c r="CN58" s="7"/>
-      <c r="CO58" s="7"/>
-      <c r="CP58" s="7"/>
-      <c r="CQ58" s="7"/>
-      <c r="CR58" s="7"/>
-      <c r="CS58" s="7"/>
-      <c r="CT58" s="7"/>
-      <c r="CU58" s="7"/>
-      <c r="CV58" s="7"/>
-      <c r="CW58" s="7"/>
-      <c r="CX58" s="7"/>
-      <c r="CY58" s="7"/>
-      <c r="CZ58" s="7"/>
-      <c r="DA58" s="7"/>
-      <c r="DB58" s="7"/>
-      <c r="DC58" s="7"/>
-      <c r="DD58" s="7"/>
-      <c r="DE58" s="7"/>
-      <c r="DF58" s="7"/>
-      <c r="DG58" s="7"/>
-      <c r="DH58" s="7"/>
-      <c r="DI58" s="7"/>
-      <c r="DJ58" s="7"/>
-      <c r="DK58" s="7"/>
-      <c r="DL58" s="7"/>
-      <c r="DM58" s="7"/>
-      <c r="DN58" s="7"/>
-      <c r="DO58" s="7"/>
-      <c r="DP58" s="7"/>
-      <c r="DQ58" s="7"/>
-      <c r="DR58" s="7"/>
-      <c r="DS58" s="7"/>
-      <c r="DT58" s="7"/>
-      <c r="DU58" s="7"/>
-      <c r="DV58" s="7"/>
-      <c r="DW58" s="7"/>
-      <c r="DX58" s="7"/>
-      <c r="DY58" s="7"/>
-      <c r="DZ58" s="7"/>
-      <c r="EA58" s="7"/>
-      <c r="EB58" s="7"/>
-      <c r="EC58" s="7"/>
-      <c r="ED58" s="7"/>
-      <c r="EE58" s="7"/>
-      <c r="EF58" s="7"/>
-      <c r="EG58" s="7"/>
-      <c r="EH58" s="7"/>
-      <c r="EI58" s="7"/>
-      <c r="EJ58" s="7"/>
-      <c r="EK58" s="7"/>
-      <c r="EL58" s="7"/>
-      <c r="EM58" s="7"/>
-      <c r="EN58" s="7"/>
-      <c r="EO58" s="7"/>
-      <c r="EP58" s="7"/>
-      <c r="EQ58" s="7"/>
-      <c r="ER58" s="7"/>
-      <c r="ES58" s="7"/>
-      <c r="ET58" s="7"/>
-      <c r="EU58" s="7"/>
-      <c r="EV58" s="7"/>
-      <c r="EW58" s="7"/>
-      <c r="EX58" s="7"/>
-      <c r="EY58" s="7"/>
-      <c r="EZ58" s="7"/>
-      <c r="FA58" s="7"/>
-      <c r="FB58" s="7"/>
-      <c r="FC58" s="7"/>
-      <c r="FD58" s="7"/>
-      <c r="FE58" s="7"/>
-      <c r="FF58" s="7"/>
-      <c r="FG58" s="7"/>
-      <c r="FH58" s="7"/>
-      <c r="FI58" s="7"/>
-      <c r="FJ58" s="7"/>
-      <c r="FK58" s="7"/>
-      <c r="FL58" s="7"/>
-      <c r="FM58" s="7"/>
-      <c r="FN58" s="7"/>
-      <c r="FO58" s="7"/>
-      <c r="FP58" s="7"/>
-      <c r="FQ58" s="7"/>
-      <c r="FR58" s="7"/>
-      <c r="FS58" s="7"/>
-      <c r="FT58" s="7"/>
-      <c r="FU58" s="7"/>
-      <c r="FV58" s="7"/>
-      <c r="FW58" s="7"/>
-      <c r="FX58" s="7"/>
-      <c r="FY58" s="7"/>
-      <c r="FZ58" s="7"/>
-      <c r="GA58" s="7"/>
-      <c r="GB58" s="7"/>
-      <c r="GC58" s="7"/>
-      <c r="GD58" s="7"/>
-      <c r="GE58" s="7"/>
-      <c r="GF58" s="7"/>
-      <c r="GG58" s="7"/>
-      <c r="GH58" s="7"/>
-      <c r="GI58" s="7"/>
-      <c r="GJ58" s="7"/>
-      <c r="GK58" s="7"/>
-      <c r="GL58" s="7"/>
-      <c r="GM58" s="7"/>
-      <c r="GN58" s="7"/>
-      <c r="GO58" s="7"/>
-      <c r="GP58" s="7"/>
-      <c r="GQ58" s="7"/>
-      <c r="GR58" s="7"/>
-      <c r="GS58" s="7"/>
-      <c r="GT58" s="7"/>
-      <c r="GU58" s="7"/>
-      <c r="GV58" s="7"/>
-      <c r="GW58" s="7"/>
-      <c r="GX58" s="7"/>
-      <c r="GY58" s="7"/>
-      <c r="GZ58" s="7"/>
-      <c r="HA58" s="7"/>
-      <c r="HB58" s="7"/>
-      <c r="HC58" s="7"/>
-      <c r="HD58" s="7"/>
-      <c r="HE58" s="7"/>
-      <c r="HF58" s="7"/>
-      <c r="HG58" s="7"/>
-      <c r="HH58" s="7"/>
-      <c r="HI58" s="7"/>
-      <c r="HJ58" s="7"/>
-      <c r="HK58" s="7"/>
-      <c r="HL58" s="7"/>
-      <c r="HM58" s="7"/>
-      <c r="HN58" s="7"/>
-      <c r="HO58" s="7"/>
-      <c r="HP58" s="7"/>
-      <c r="HQ58" s="7"/>
-      <c r="HR58" s="7"/>
-      <c r="HS58" s="7"/>
-      <c r="HT58" s="7"/>
-      <c r="HU58" s="7"/>
-      <c r="HV58" s="7"/>
-      <c r="HW58" s="7"/>
-      <c r="HX58" s="7"/>
-      <c r="HY58" s="7"/>
-      <c r="HZ58" s="7"/>
-      <c r="IA58" s="7"/>
-      <c r="IB58" s="7"/>
-      <c r="IC58" s="7"/>
-    </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="59" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="32"/>
       <c r="B59" s="31" t="n">
         <f aca="false">B58+1</f>
@@ -13158,8 +13124,240 @@
         <v>31</v>
       </c>
       <c r="E59" s="33"/>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
+      <c r="M59" s="7"/>
+      <c r="N59" s="7"/>
+      <c r="O59" s="7"/>
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
+      <c r="R59" s="7"/>
+      <c r="S59" s="7"/>
+      <c r="T59" s="7"/>
+      <c r="U59" s="7"/>
+      <c r="V59" s="7"/>
+      <c r="W59" s="7"/>
+      <c r="X59" s="7"/>
+      <c r="Y59" s="7"/>
+      <c r="Z59" s="7"/>
+      <c r="AA59" s="7"/>
+      <c r="AB59" s="7"/>
+      <c r="AC59" s="7"/>
+      <c r="AD59" s="7"/>
+      <c r="AE59" s="7"/>
+      <c r="AF59" s="7"/>
+      <c r="AG59" s="7"/>
+      <c r="AH59" s="7"/>
+      <c r="AI59" s="7"/>
+      <c r="AJ59" s="7"/>
+      <c r="AK59" s="7"/>
+      <c r="AL59" s="7"/>
+      <c r="AM59" s="7"/>
+      <c r="AN59" s="7"/>
+      <c r="AO59" s="7"/>
+      <c r="AP59" s="7"/>
+      <c r="AQ59" s="7"/>
+      <c r="AR59" s="7"/>
+      <c r="AS59" s="7"/>
+      <c r="AT59" s="7"/>
+      <c r="AU59" s="7"/>
+      <c r="AV59" s="7"/>
+      <c r="AW59" s="7"/>
+      <c r="AX59" s="7"/>
+      <c r="AY59" s="7"/>
+      <c r="AZ59" s="7"/>
+      <c r="BA59" s="7"/>
+      <c r="BB59" s="7"/>
+      <c r="BC59" s="7"/>
+      <c r="BD59" s="7"/>
+      <c r="BE59" s="7"/>
+      <c r="BF59" s="7"/>
+      <c r="BG59" s="7"/>
+      <c r="BH59" s="7"/>
+      <c r="BI59" s="7"/>
+      <c r="BJ59" s="7"/>
+      <c r="BK59" s="7"/>
+      <c r="BL59" s="7"/>
+      <c r="BM59" s="7"/>
+      <c r="BN59" s="7"/>
+      <c r="BO59" s="7"/>
+      <c r="BP59" s="7"/>
+      <c r="BQ59" s="7"/>
+      <c r="BR59" s="7"/>
+      <c r="BS59" s="7"/>
+      <c r="BT59" s="7"/>
+      <c r="BU59" s="7"/>
+      <c r="BV59" s="7"/>
+      <c r="BW59" s="7"/>
+      <c r="BX59" s="7"/>
+      <c r="BY59" s="7"/>
+      <c r="BZ59" s="7"/>
+      <c r="CA59" s="7"/>
+      <c r="CB59" s="7"/>
+      <c r="CC59" s="7"/>
+      <c r="CD59" s="7"/>
+      <c r="CE59" s="7"/>
+      <c r="CF59" s="7"/>
+      <c r="CG59" s="7"/>
+      <c r="CH59" s="7"/>
+      <c r="CI59" s="7"/>
+      <c r="CJ59" s="7"/>
+      <c r="CK59" s="7"/>
+      <c r="CL59" s="7"/>
+      <c r="CM59" s="7"/>
+      <c r="CN59" s="7"/>
+      <c r="CO59" s="7"/>
+      <c r="CP59" s="7"/>
+      <c r="CQ59" s="7"/>
+      <c r="CR59" s="7"/>
+      <c r="CS59" s="7"/>
+      <c r="CT59" s="7"/>
+      <c r="CU59" s="7"/>
+      <c r="CV59" s="7"/>
+      <c r="CW59" s="7"/>
+      <c r="CX59" s="7"/>
+      <c r="CY59" s="7"/>
+      <c r="CZ59" s="7"/>
+      <c r="DA59" s="7"/>
+      <c r="DB59" s="7"/>
+      <c r="DC59" s="7"/>
+      <c r="DD59" s="7"/>
+      <c r="DE59" s="7"/>
+      <c r="DF59" s="7"/>
+      <c r="DG59" s="7"/>
+      <c r="DH59" s="7"/>
+      <c r="DI59" s="7"/>
+      <c r="DJ59" s="7"/>
+      <c r="DK59" s="7"/>
+      <c r="DL59" s="7"/>
+      <c r="DM59" s="7"/>
+      <c r="DN59" s="7"/>
+      <c r="DO59" s="7"/>
+      <c r="DP59" s="7"/>
+      <c r="DQ59" s="7"/>
+      <c r="DR59" s="7"/>
+      <c r="DS59" s="7"/>
+      <c r="DT59" s="7"/>
+      <c r="DU59" s="7"/>
+      <c r="DV59" s="7"/>
+      <c r="DW59" s="7"/>
+      <c r="DX59" s="7"/>
+      <c r="DY59" s="7"/>
+      <c r="DZ59" s="7"/>
+      <c r="EA59" s="7"/>
+      <c r="EB59" s="7"/>
+      <c r="EC59" s="7"/>
+      <c r="ED59" s="7"/>
+      <c r="EE59" s="7"/>
+      <c r="EF59" s="7"/>
+      <c r="EG59" s="7"/>
+      <c r="EH59" s="7"/>
+      <c r="EI59" s="7"/>
+      <c r="EJ59" s="7"/>
+      <c r="EK59" s="7"/>
+      <c r="EL59" s="7"/>
+      <c r="EM59" s="7"/>
+      <c r="EN59" s="7"/>
+      <c r="EO59" s="7"/>
+      <c r="EP59" s="7"/>
+      <c r="EQ59" s="7"/>
+      <c r="ER59" s="7"/>
+      <c r="ES59" s="7"/>
+      <c r="ET59" s="7"/>
+      <c r="EU59" s="7"/>
+      <c r="EV59" s="7"/>
+      <c r="EW59" s="7"/>
+      <c r="EX59" s="7"/>
+      <c r="EY59" s="7"/>
+      <c r="EZ59" s="7"/>
+      <c r="FA59" s="7"/>
+      <c r="FB59" s="7"/>
+      <c r="FC59" s="7"/>
+      <c r="FD59" s="7"/>
+      <c r="FE59" s="7"/>
+      <c r="FF59" s="7"/>
+      <c r="FG59" s="7"/>
+      <c r="FH59" s="7"/>
+      <c r="FI59" s="7"/>
+      <c r="FJ59" s="7"/>
+      <c r="FK59" s="7"/>
+      <c r="FL59" s="7"/>
+      <c r="FM59" s="7"/>
+      <c r="FN59" s="7"/>
+      <c r="FO59" s="7"/>
+      <c r="FP59" s="7"/>
+      <c r="FQ59" s="7"/>
+      <c r="FR59" s="7"/>
+      <c r="FS59" s="7"/>
+      <c r="FT59" s="7"/>
+      <c r="FU59" s="7"/>
+      <c r="FV59" s="7"/>
+      <c r="FW59" s="7"/>
+      <c r="FX59" s="7"/>
+      <c r="FY59" s="7"/>
+      <c r="FZ59" s="7"/>
+      <c r="GA59" s="7"/>
+      <c r="GB59" s="7"/>
+      <c r="GC59" s="7"/>
+      <c r="GD59" s="7"/>
+      <c r="GE59" s="7"/>
+      <c r="GF59" s="7"/>
+      <c r="GG59" s="7"/>
+      <c r="GH59" s="7"/>
+      <c r="GI59" s="7"/>
+      <c r="GJ59" s="7"/>
+      <c r="GK59" s="7"/>
+      <c r="GL59" s="7"/>
+      <c r="GM59" s="7"/>
+      <c r="GN59" s="7"/>
+      <c r="GO59" s="7"/>
+      <c r="GP59" s="7"/>
+      <c r="GQ59" s="7"/>
+      <c r="GR59" s="7"/>
+      <c r="GS59" s="7"/>
+      <c r="GT59" s="7"/>
+      <c r="GU59" s="7"/>
+      <c r="GV59" s="7"/>
+      <c r="GW59" s="7"/>
+      <c r="GX59" s="7"/>
+      <c r="GY59" s="7"/>
+      <c r="GZ59" s="7"/>
+      <c r="HA59" s="7"/>
+      <c r="HB59" s="7"/>
+      <c r="HC59" s="7"/>
+      <c r="HD59" s="7"/>
+      <c r="HE59" s="7"/>
+      <c r="HF59" s="7"/>
+      <c r="HG59" s="7"/>
+      <c r="HH59" s="7"/>
+      <c r="HI59" s="7"/>
+      <c r="HJ59" s="7"/>
+      <c r="HK59" s="7"/>
+      <c r="HL59" s="7"/>
+      <c r="HM59" s="7"/>
+      <c r="HN59" s="7"/>
+      <c r="HO59" s="7"/>
+      <c r="HP59" s="7"/>
+      <c r="HQ59" s="7"/>
+      <c r="HR59" s="7"/>
+      <c r="HS59" s="7"/>
+      <c r="HT59" s="7"/>
+      <c r="HU59" s="7"/>
+      <c r="HV59" s="7"/>
+      <c r="HW59" s="7"/>
+      <c r="HX59" s="7"/>
+      <c r="HY59" s="7"/>
+      <c r="HZ59" s="7"/>
+      <c r="IA59" s="7"/>
+      <c r="IB59" s="7"/>
+      <c r="IC59" s="7"/>
+    </row>
+    <row r="60" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="36"/>
       <c r="B60" s="35" t="n">
         <f aca="false">B59+1</f>
@@ -13172,8 +13370,240 @@
         <v>32</v>
       </c>
       <c r="E60" s="36"/>
-    </row>
-    <row r="61" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+      <c r="M60" s="7"/>
+      <c r="N60" s="7"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
+      <c r="R60" s="7"/>
+      <c r="S60" s="7"/>
+      <c r="T60" s="7"/>
+      <c r="U60" s="7"/>
+      <c r="V60" s="7"/>
+      <c r="W60" s="7"/>
+      <c r="X60" s="7"/>
+      <c r="Y60" s="7"/>
+      <c r="Z60" s="7"/>
+      <c r="AA60" s="7"/>
+      <c r="AB60" s="7"/>
+      <c r="AC60" s="7"/>
+      <c r="AD60" s="7"/>
+      <c r="AE60" s="7"/>
+      <c r="AF60" s="7"/>
+      <c r="AG60" s="7"/>
+      <c r="AH60" s="7"/>
+      <c r="AI60" s="7"/>
+      <c r="AJ60" s="7"/>
+      <c r="AK60" s="7"/>
+      <c r="AL60" s="7"/>
+      <c r="AM60" s="7"/>
+      <c r="AN60" s="7"/>
+      <c r="AO60" s="7"/>
+      <c r="AP60" s="7"/>
+      <c r="AQ60" s="7"/>
+      <c r="AR60" s="7"/>
+      <c r="AS60" s="7"/>
+      <c r="AT60" s="7"/>
+      <c r="AU60" s="7"/>
+      <c r="AV60" s="7"/>
+      <c r="AW60" s="7"/>
+      <c r="AX60" s="7"/>
+      <c r="AY60" s="7"/>
+      <c r="AZ60" s="7"/>
+      <c r="BA60" s="7"/>
+      <c r="BB60" s="7"/>
+      <c r="BC60" s="7"/>
+      <c r="BD60" s="7"/>
+      <c r="BE60" s="7"/>
+      <c r="BF60" s="7"/>
+      <c r="BG60" s="7"/>
+      <c r="BH60" s="7"/>
+      <c r="BI60" s="7"/>
+      <c r="BJ60" s="7"/>
+      <c r="BK60" s="7"/>
+      <c r="BL60" s="7"/>
+      <c r="BM60" s="7"/>
+      <c r="BN60" s="7"/>
+      <c r="BO60" s="7"/>
+      <c r="BP60" s="7"/>
+      <c r="BQ60" s="7"/>
+      <c r="BR60" s="7"/>
+      <c r="BS60" s="7"/>
+      <c r="BT60" s="7"/>
+      <c r="BU60" s="7"/>
+      <c r="BV60" s="7"/>
+      <c r="BW60" s="7"/>
+      <c r="BX60" s="7"/>
+      <c r="BY60" s="7"/>
+      <c r="BZ60" s="7"/>
+      <c r="CA60" s="7"/>
+      <c r="CB60" s="7"/>
+      <c r="CC60" s="7"/>
+      <c r="CD60" s="7"/>
+      <c r="CE60" s="7"/>
+      <c r="CF60" s="7"/>
+      <c r="CG60" s="7"/>
+      <c r="CH60" s="7"/>
+      <c r="CI60" s="7"/>
+      <c r="CJ60" s="7"/>
+      <c r="CK60" s="7"/>
+      <c r="CL60" s="7"/>
+      <c r="CM60" s="7"/>
+      <c r="CN60" s="7"/>
+      <c r="CO60" s="7"/>
+      <c r="CP60" s="7"/>
+      <c r="CQ60" s="7"/>
+      <c r="CR60" s="7"/>
+      <c r="CS60" s="7"/>
+      <c r="CT60" s="7"/>
+      <c r="CU60" s="7"/>
+      <c r="CV60" s="7"/>
+      <c r="CW60" s="7"/>
+      <c r="CX60" s="7"/>
+      <c r="CY60" s="7"/>
+      <c r="CZ60" s="7"/>
+      <c r="DA60" s="7"/>
+      <c r="DB60" s="7"/>
+      <c r="DC60" s="7"/>
+      <c r="DD60" s="7"/>
+      <c r="DE60" s="7"/>
+      <c r="DF60" s="7"/>
+      <c r="DG60" s="7"/>
+      <c r="DH60" s="7"/>
+      <c r="DI60" s="7"/>
+      <c r="DJ60" s="7"/>
+      <c r="DK60" s="7"/>
+      <c r="DL60" s="7"/>
+      <c r="DM60" s="7"/>
+      <c r="DN60" s="7"/>
+      <c r="DO60" s="7"/>
+      <c r="DP60" s="7"/>
+      <c r="DQ60" s="7"/>
+      <c r="DR60" s="7"/>
+      <c r="DS60" s="7"/>
+      <c r="DT60" s="7"/>
+      <c r="DU60" s="7"/>
+      <c r="DV60" s="7"/>
+      <c r="DW60" s="7"/>
+      <c r="DX60" s="7"/>
+      <c r="DY60" s="7"/>
+      <c r="DZ60" s="7"/>
+      <c r="EA60" s="7"/>
+      <c r="EB60" s="7"/>
+      <c r="EC60" s="7"/>
+      <c r="ED60" s="7"/>
+      <c r="EE60" s="7"/>
+      <c r="EF60" s="7"/>
+      <c r="EG60" s="7"/>
+      <c r="EH60" s="7"/>
+      <c r="EI60" s="7"/>
+      <c r="EJ60" s="7"/>
+      <c r="EK60" s="7"/>
+      <c r="EL60" s="7"/>
+      <c r="EM60" s="7"/>
+      <c r="EN60" s="7"/>
+      <c r="EO60" s="7"/>
+      <c r="EP60" s="7"/>
+      <c r="EQ60" s="7"/>
+      <c r="ER60" s="7"/>
+      <c r="ES60" s="7"/>
+      <c r="ET60" s="7"/>
+      <c r="EU60" s="7"/>
+      <c r="EV60" s="7"/>
+      <c r="EW60" s="7"/>
+      <c r="EX60" s="7"/>
+      <c r="EY60" s="7"/>
+      <c r="EZ60" s="7"/>
+      <c r="FA60" s="7"/>
+      <c r="FB60" s="7"/>
+      <c r="FC60" s="7"/>
+      <c r="FD60" s="7"/>
+      <c r="FE60" s="7"/>
+      <c r="FF60" s="7"/>
+      <c r="FG60" s="7"/>
+      <c r="FH60" s="7"/>
+      <c r="FI60" s="7"/>
+      <c r="FJ60" s="7"/>
+      <c r="FK60" s="7"/>
+      <c r="FL60" s="7"/>
+      <c r="FM60" s="7"/>
+      <c r="FN60" s="7"/>
+      <c r="FO60" s="7"/>
+      <c r="FP60" s="7"/>
+      <c r="FQ60" s="7"/>
+      <c r="FR60" s="7"/>
+      <c r="FS60" s="7"/>
+      <c r="FT60" s="7"/>
+      <c r="FU60" s="7"/>
+      <c r="FV60" s="7"/>
+      <c r="FW60" s="7"/>
+      <c r="FX60" s="7"/>
+      <c r="FY60" s="7"/>
+      <c r="FZ60" s="7"/>
+      <c r="GA60" s="7"/>
+      <c r="GB60" s="7"/>
+      <c r="GC60" s="7"/>
+      <c r="GD60" s="7"/>
+      <c r="GE60" s="7"/>
+      <c r="GF60" s="7"/>
+      <c r="GG60" s="7"/>
+      <c r="GH60" s="7"/>
+      <c r="GI60" s="7"/>
+      <c r="GJ60" s="7"/>
+      <c r="GK60" s="7"/>
+      <c r="GL60" s="7"/>
+      <c r="GM60" s="7"/>
+      <c r="GN60" s="7"/>
+      <c r="GO60" s="7"/>
+      <c r="GP60" s="7"/>
+      <c r="GQ60" s="7"/>
+      <c r="GR60" s="7"/>
+      <c r="GS60" s="7"/>
+      <c r="GT60" s="7"/>
+      <c r="GU60" s="7"/>
+      <c r="GV60" s="7"/>
+      <c r="GW60" s="7"/>
+      <c r="GX60" s="7"/>
+      <c r="GY60" s="7"/>
+      <c r="GZ60" s="7"/>
+      <c r="HA60" s="7"/>
+      <c r="HB60" s="7"/>
+      <c r="HC60" s="7"/>
+      <c r="HD60" s="7"/>
+      <c r="HE60" s="7"/>
+      <c r="HF60" s="7"/>
+      <c r="HG60" s="7"/>
+      <c r="HH60" s="7"/>
+      <c r="HI60" s="7"/>
+      <c r="HJ60" s="7"/>
+      <c r="HK60" s="7"/>
+      <c r="HL60" s="7"/>
+      <c r="HM60" s="7"/>
+      <c r="HN60" s="7"/>
+      <c r="HO60" s="7"/>
+      <c r="HP60" s="7"/>
+      <c r="HQ60" s="7"/>
+      <c r="HR60" s="7"/>
+      <c r="HS60" s="7"/>
+      <c r="HT60" s="7"/>
+      <c r="HU60" s="7"/>
+      <c r="HV60" s="7"/>
+      <c r="HW60" s="7"/>
+      <c r="HX60" s="7"/>
+      <c r="HY60" s="7"/>
+      <c r="HZ60" s="7"/>
+      <c r="IA60" s="7"/>
+      <c r="IB60" s="7"/>
+      <c r="IC60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="36"/>
       <c r="B61" s="35" t="n">
         <f aca="false">B60+1</f>
@@ -13186,240 +13616,8 @@
         <v>33</v>
       </c>
       <c r="E61" s="36"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
-      <c r="L61" s="7"/>
-      <c r="M61" s="7"/>
-      <c r="N61" s="7"/>
-      <c r="O61" s="7"/>
-      <c r="P61" s="7"/>
-      <c r="Q61" s="7"/>
-      <c r="R61" s="7"/>
-      <c r="S61" s="7"/>
-      <c r="T61" s="7"/>
-      <c r="U61" s="7"/>
-      <c r="V61" s="7"/>
-      <c r="W61" s="7"/>
-      <c r="X61" s="7"/>
-      <c r="Y61" s="7"/>
-      <c r="Z61" s="7"/>
-      <c r="AA61" s="7"/>
-      <c r="AB61" s="7"/>
-      <c r="AC61" s="7"/>
-      <c r="AD61" s="7"/>
-      <c r="AE61" s="7"/>
-      <c r="AF61" s="7"/>
-      <c r="AG61" s="7"/>
-      <c r="AH61" s="7"/>
-      <c r="AI61" s="7"/>
-      <c r="AJ61" s="7"/>
-      <c r="AK61" s="7"/>
-      <c r="AL61" s="7"/>
-      <c r="AM61" s="7"/>
-      <c r="AN61" s="7"/>
-      <c r="AO61" s="7"/>
-      <c r="AP61" s="7"/>
-      <c r="AQ61" s="7"/>
-      <c r="AR61" s="7"/>
-      <c r="AS61" s="7"/>
-      <c r="AT61" s="7"/>
-      <c r="AU61" s="7"/>
-      <c r="AV61" s="7"/>
-      <c r="AW61" s="7"/>
-      <c r="AX61" s="7"/>
-      <c r="AY61" s="7"/>
-      <c r="AZ61" s="7"/>
-      <c r="BA61" s="7"/>
-      <c r="BB61" s="7"/>
-      <c r="BC61" s="7"/>
-      <c r="BD61" s="7"/>
-      <c r="BE61" s="7"/>
-      <c r="BF61" s="7"/>
-      <c r="BG61" s="7"/>
-      <c r="BH61" s="7"/>
-      <c r="BI61" s="7"/>
-      <c r="BJ61" s="7"/>
-      <c r="BK61" s="7"/>
-      <c r="BL61" s="7"/>
-      <c r="BM61" s="7"/>
-      <c r="BN61" s="7"/>
-      <c r="BO61" s="7"/>
-      <c r="BP61" s="7"/>
-      <c r="BQ61" s="7"/>
-      <c r="BR61" s="7"/>
-      <c r="BS61" s="7"/>
-      <c r="BT61" s="7"/>
-      <c r="BU61" s="7"/>
-      <c r="BV61" s="7"/>
-      <c r="BW61" s="7"/>
-      <c r="BX61" s="7"/>
-      <c r="BY61" s="7"/>
-      <c r="BZ61" s="7"/>
-      <c r="CA61" s="7"/>
-      <c r="CB61" s="7"/>
-      <c r="CC61" s="7"/>
-      <c r="CD61" s="7"/>
-      <c r="CE61" s="7"/>
-      <c r="CF61" s="7"/>
-      <c r="CG61" s="7"/>
-      <c r="CH61" s="7"/>
-      <c r="CI61" s="7"/>
-      <c r="CJ61" s="7"/>
-      <c r="CK61" s="7"/>
-      <c r="CL61" s="7"/>
-      <c r="CM61" s="7"/>
-      <c r="CN61" s="7"/>
-      <c r="CO61" s="7"/>
-      <c r="CP61" s="7"/>
-      <c r="CQ61" s="7"/>
-      <c r="CR61" s="7"/>
-      <c r="CS61" s="7"/>
-      <c r="CT61" s="7"/>
-      <c r="CU61" s="7"/>
-      <c r="CV61" s="7"/>
-      <c r="CW61" s="7"/>
-      <c r="CX61" s="7"/>
-      <c r="CY61" s="7"/>
-      <c r="CZ61" s="7"/>
-      <c r="DA61" s="7"/>
-      <c r="DB61" s="7"/>
-      <c r="DC61" s="7"/>
-      <c r="DD61" s="7"/>
-      <c r="DE61" s="7"/>
-      <c r="DF61" s="7"/>
-      <c r="DG61" s="7"/>
-      <c r="DH61" s="7"/>
-      <c r="DI61" s="7"/>
-      <c r="DJ61" s="7"/>
-      <c r="DK61" s="7"/>
-      <c r="DL61" s="7"/>
-      <c r="DM61" s="7"/>
-      <c r="DN61" s="7"/>
-      <c r="DO61" s="7"/>
-      <c r="DP61" s="7"/>
-      <c r="DQ61" s="7"/>
-      <c r="DR61" s="7"/>
-      <c r="DS61" s="7"/>
-      <c r="DT61" s="7"/>
-      <c r="DU61" s="7"/>
-      <c r="DV61" s="7"/>
-      <c r="DW61" s="7"/>
-      <c r="DX61" s="7"/>
-      <c r="DY61" s="7"/>
-      <c r="DZ61" s="7"/>
-      <c r="EA61" s="7"/>
-      <c r="EB61" s="7"/>
-      <c r="EC61" s="7"/>
-      <c r="ED61" s="7"/>
-      <c r="EE61" s="7"/>
-      <c r="EF61" s="7"/>
-      <c r="EG61" s="7"/>
-      <c r="EH61" s="7"/>
-      <c r="EI61" s="7"/>
-      <c r="EJ61" s="7"/>
-      <c r="EK61" s="7"/>
-      <c r="EL61" s="7"/>
-      <c r="EM61" s="7"/>
-      <c r="EN61" s="7"/>
-      <c r="EO61" s="7"/>
-      <c r="EP61" s="7"/>
-      <c r="EQ61" s="7"/>
-      <c r="ER61" s="7"/>
-      <c r="ES61" s="7"/>
-      <c r="ET61" s="7"/>
-      <c r="EU61" s="7"/>
-      <c r="EV61" s="7"/>
-      <c r="EW61" s="7"/>
-      <c r="EX61" s="7"/>
-      <c r="EY61" s="7"/>
-      <c r="EZ61" s="7"/>
-      <c r="FA61" s="7"/>
-      <c r="FB61" s="7"/>
-      <c r="FC61" s="7"/>
-      <c r="FD61" s="7"/>
-      <c r="FE61" s="7"/>
-      <c r="FF61" s="7"/>
-      <c r="FG61" s="7"/>
-      <c r="FH61" s="7"/>
-      <c r="FI61" s="7"/>
-      <c r="FJ61" s="7"/>
-      <c r="FK61" s="7"/>
-      <c r="FL61" s="7"/>
-      <c r="FM61" s="7"/>
-      <c r="FN61" s="7"/>
-      <c r="FO61" s="7"/>
-      <c r="FP61" s="7"/>
-      <c r="FQ61" s="7"/>
-      <c r="FR61" s="7"/>
-      <c r="FS61" s="7"/>
-      <c r="FT61" s="7"/>
-      <c r="FU61" s="7"/>
-      <c r="FV61" s="7"/>
-      <c r="FW61" s="7"/>
-      <c r="FX61" s="7"/>
-      <c r="FY61" s="7"/>
-      <c r="FZ61" s="7"/>
-      <c r="GA61" s="7"/>
-      <c r="GB61" s="7"/>
-      <c r="GC61" s="7"/>
-      <c r="GD61" s="7"/>
-      <c r="GE61" s="7"/>
-      <c r="GF61" s="7"/>
-      <c r="GG61" s="7"/>
-      <c r="GH61" s="7"/>
-      <c r="GI61" s="7"/>
-      <c r="GJ61" s="7"/>
-      <c r="GK61" s="7"/>
-      <c r="GL61" s="7"/>
-      <c r="GM61" s="7"/>
-      <c r="GN61" s="7"/>
-      <c r="GO61" s="7"/>
-      <c r="GP61" s="7"/>
-      <c r="GQ61" s="7"/>
-      <c r="GR61" s="7"/>
-      <c r="GS61" s="7"/>
-      <c r="GT61" s="7"/>
-      <c r="GU61" s="7"/>
-      <c r="GV61" s="7"/>
-      <c r="GW61" s="7"/>
-      <c r="GX61" s="7"/>
-      <c r="GY61" s="7"/>
-      <c r="GZ61" s="7"/>
-      <c r="HA61" s="7"/>
-      <c r="HB61" s="7"/>
-      <c r="HC61" s="7"/>
-      <c r="HD61" s="7"/>
-      <c r="HE61" s="7"/>
-      <c r="HF61" s="7"/>
-      <c r="HG61" s="7"/>
-      <c r="HH61" s="7"/>
-      <c r="HI61" s="7"/>
-      <c r="HJ61" s="7"/>
-      <c r="HK61" s="7"/>
-      <c r="HL61" s="7"/>
-      <c r="HM61" s="7"/>
-      <c r="HN61" s="7"/>
-      <c r="HO61" s="7"/>
-      <c r="HP61" s="7"/>
-      <c r="HQ61" s="7"/>
-      <c r="HR61" s="7"/>
-      <c r="HS61" s="7"/>
-      <c r="HT61" s="7"/>
-      <c r="HU61" s="7"/>
-      <c r="HV61" s="7"/>
-      <c r="HW61" s="7"/>
-      <c r="HX61" s="7"/>
-      <c r="HY61" s="7"/>
-      <c r="HZ61" s="7"/>
-      <c r="IA61" s="7"/>
-      <c r="IB61" s="7"/>
-      <c r="IC61" s="7"/>
-    </row>
-    <row r="62" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="40"/>
       <c r="B62" s="39" t="n">
         <f aca="false">B61+1</f>
@@ -13432,240 +13630,8 @@
         <v>34</v>
       </c>
       <c r="E62" s="40"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="7"/>
-      <c r="O62" s="7"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="7"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="7"/>
-      <c r="T62" s="7"/>
-      <c r="U62" s="7"/>
-      <c r="V62" s="7"/>
-      <c r="W62" s="7"/>
-      <c r="X62" s="7"/>
-      <c r="Y62" s="7"/>
-      <c r="Z62" s="7"/>
-      <c r="AA62" s="7"/>
-      <c r="AB62" s="7"/>
-      <c r="AC62" s="7"/>
-      <c r="AD62" s="7"/>
-      <c r="AE62" s="7"/>
-      <c r="AF62" s="7"/>
-      <c r="AG62" s="7"/>
-      <c r="AH62" s="7"/>
-      <c r="AI62" s="7"/>
-      <c r="AJ62" s="7"/>
-      <c r="AK62" s="7"/>
-      <c r="AL62" s="7"/>
-      <c r="AM62" s="7"/>
-      <c r="AN62" s="7"/>
-      <c r="AO62" s="7"/>
-      <c r="AP62" s="7"/>
-      <c r="AQ62" s="7"/>
-      <c r="AR62" s="7"/>
-      <c r="AS62" s="7"/>
-      <c r="AT62" s="7"/>
-      <c r="AU62" s="7"/>
-      <c r="AV62" s="7"/>
-      <c r="AW62" s="7"/>
-      <c r="AX62" s="7"/>
-      <c r="AY62" s="7"/>
-      <c r="AZ62" s="7"/>
-      <c r="BA62" s="7"/>
-      <c r="BB62" s="7"/>
-      <c r="BC62" s="7"/>
-      <c r="BD62" s="7"/>
-      <c r="BE62" s="7"/>
-      <c r="BF62" s="7"/>
-      <c r="BG62" s="7"/>
-      <c r="BH62" s="7"/>
-      <c r="BI62" s="7"/>
-      <c r="BJ62" s="7"/>
-      <c r="BK62" s="7"/>
-      <c r="BL62" s="7"/>
-      <c r="BM62" s="7"/>
-      <c r="BN62" s="7"/>
-      <c r="BO62" s="7"/>
-      <c r="BP62" s="7"/>
-      <c r="BQ62" s="7"/>
-      <c r="BR62" s="7"/>
-      <c r="BS62" s="7"/>
-      <c r="BT62" s="7"/>
-      <c r="BU62" s="7"/>
-      <c r="BV62" s="7"/>
-      <c r="BW62" s="7"/>
-      <c r="BX62" s="7"/>
-      <c r="BY62" s="7"/>
-      <c r="BZ62" s="7"/>
-      <c r="CA62" s="7"/>
-      <c r="CB62" s="7"/>
-      <c r="CC62" s="7"/>
-      <c r="CD62" s="7"/>
-      <c r="CE62" s="7"/>
-      <c r="CF62" s="7"/>
-      <c r="CG62" s="7"/>
-      <c r="CH62" s="7"/>
-      <c r="CI62" s="7"/>
-      <c r="CJ62" s="7"/>
-      <c r="CK62" s="7"/>
-      <c r="CL62" s="7"/>
-      <c r="CM62" s="7"/>
-      <c r="CN62" s="7"/>
-      <c r="CO62" s="7"/>
-      <c r="CP62" s="7"/>
-      <c r="CQ62" s="7"/>
-      <c r="CR62" s="7"/>
-      <c r="CS62" s="7"/>
-      <c r="CT62" s="7"/>
-      <c r="CU62" s="7"/>
-      <c r="CV62" s="7"/>
-      <c r="CW62" s="7"/>
-      <c r="CX62" s="7"/>
-      <c r="CY62" s="7"/>
-      <c r="CZ62" s="7"/>
-      <c r="DA62" s="7"/>
-      <c r="DB62" s="7"/>
-      <c r="DC62" s="7"/>
-      <c r="DD62" s="7"/>
-      <c r="DE62" s="7"/>
-      <c r="DF62" s="7"/>
-      <c r="DG62" s="7"/>
-      <c r="DH62" s="7"/>
-      <c r="DI62" s="7"/>
-      <c r="DJ62" s="7"/>
-      <c r="DK62" s="7"/>
-      <c r="DL62" s="7"/>
-      <c r="DM62" s="7"/>
-      <c r="DN62" s="7"/>
-      <c r="DO62" s="7"/>
-      <c r="DP62" s="7"/>
-      <c r="DQ62" s="7"/>
-      <c r="DR62" s="7"/>
-      <c r="DS62" s="7"/>
-      <c r="DT62" s="7"/>
-      <c r="DU62" s="7"/>
-      <c r="DV62" s="7"/>
-      <c r="DW62" s="7"/>
-      <c r="DX62" s="7"/>
-      <c r="DY62" s="7"/>
-      <c r="DZ62" s="7"/>
-      <c r="EA62" s="7"/>
-      <c r="EB62" s="7"/>
-      <c r="EC62" s="7"/>
-      <c r="ED62" s="7"/>
-      <c r="EE62" s="7"/>
-      <c r="EF62" s="7"/>
-      <c r="EG62" s="7"/>
-      <c r="EH62" s="7"/>
-      <c r="EI62" s="7"/>
-      <c r="EJ62" s="7"/>
-      <c r="EK62" s="7"/>
-      <c r="EL62" s="7"/>
-      <c r="EM62" s="7"/>
-      <c r="EN62" s="7"/>
-      <c r="EO62" s="7"/>
-      <c r="EP62" s="7"/>
-      <c r="EQ62" s="7"/>
-      <c r="ER62" s="7"/>
-      <c r="ES62" s="7"/>
-      <c r="ET62" s="7"/>
-      <c r="EU62" s="7"/>
-      <c r="EV62" s="7"/>
-      <c r="EW62" s="7"/>
-      <c r="EX62" s="7"/>
-      <c r="EY62" s="7"/>
-      <c r="EZ62" s="7"/>
-      <c r="FA62" s="7"/>
-      <c r="FB62" s="7"/>
-      <c r="FC62" s="7"/>
-      <c r="FD62" s="7"/>
-      <c r="FE62" s="7"/>
-      <c r="FF62" s="7"/>
-      <c r="FG62" s="7"/>
-      <c r="FH62" s="7"/>
-      <c r="FI62" s="7"/>
-      <c r="FJ62" s="7"/>
-      <c r="FK62" s="7"/>
-      <c r="FL62" s="7"/>
-      <c r="FM62" s="7"/>
-      <c r="FN62" s="7"/>
-      <c r="FO62" s="7"/>
-      <c r="FP62" s="7"/>
-      <c r="FQ62" s="7"/>
-      <c r="FR62" s="7"/>
-      <c r="FS62" s="7"/>
-      <c r="FT62" s="7"/>
-      <c r="FU62" s="7"/>
-      <c r="FV62" s="7"/>
-      <c r="FW62" s="7"/>
-      <c r="FX62" s="7"/>
-      <c r="FY62" s="7"/>
-      <c r="FZ62" s="7"/>
-      <c r="GA62" s="7"/>
-      <c r="GB62" s="7"/>
-      <c r="GC62" s="7"/>
-      <c r="GD62" s="7"/>
-      <c r="GE62" s="7"/>
-      <c r="GF62" s="7"/>
-      <c r="GG62" s="7"/>
-      <c r="GH62" s="7"/>
-      <c r="GI62" s="7"/>
-      <c r="GJ62" s="7"/>
-      <c r="GK62" s="7"/>
-      <c r="GL62" s="7"/>
-      <c r="GM62" s="7"/>
-      <c r="GN62" s="7"/>
-      <c r="GO62" s="7"/>
-      <c r="GP62" s="7"/>
-      <c r="GQ62" s="7"/>
-      <c r="GR62" s="7"/>
-      <c r="GS62" s="7"/>
-      <c r="GT62" s="7"/>
-      <c r="GU62" s="7"/>
-      <c r="GV62" s="7"/>
-      <c r="GW62" s="7"/>
-      <c r="GX62" s="7"/>
-      <c r="GY62" s="7"/>
-      <c r="GZ62" s="7"/>
-      <c r="HA62" s="7"/>
-      <c r="HB62" s="7"/>
-      <c r="HC62" s="7"/>
-      <c r="HD62" s="7"/>
-      <c r="HE62" s="7"/>
-      <c r="HF62" s="7"/>
-      <c r="HG62" s="7"/>
-      <c r="HH62" s="7"/>
-      <c r="HI62" s="7"/>
-      <c r="HJ62" s="7"/>
-      <c r="HK62" s="7"/>
-      <c r="HL62" s="7"/>
-      <c r="HM62" s="7"/>
-      <c r="HN62" s="7"/>
-      <c r="HO62" s="7"/>
-      <c r="HP62" s="7"/>
-      <c r="HQ62" s="7"/>
-      <c r="HR62" s="7"/>
-      <c r="HS62" s="7"/>
-      <c r="HT62" s="7"/>
-      <c r="HU62" s="7"/>
-      <c r="HV62" s="7"/>
-      <c r="HW62" s="7"/>
-      <c r="HX62" s="7"/>
-      <c r="HY62" s="7"/>
-      <c r="HZ62" s="7"/>
-      <c r="IA62" s="7"/>
-      <c r="IB62" s="7"/>
-      <c r="IC62" s="7"/>
-    </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="63" s="34" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="36"/>
       <c r="B63" s="35" t="n">
         <f aca="false">B62+1</f>
@@ -13678,6 +13644,238 @@
         <v>35</v>
       </c>
       <c r="E63" s="36"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
+      <c r="M63" s="7"/>
+      <c r="N63" s="7"/>
+      <c r="O63" s="7"/>
+      <c r="P63" s="7"/>
+      <c r="Q63" s="7"/>
+      <c r="R63" s="7"/>
+      <c r="S63" s="7"/>
+      <c r="T63" s="7"/>
+      <c r="U63" s="7"/>
+      <c r="V63" s="7"/>
+      <c r="W63" s="7"/>
+      <c r="X63" s="7"/>
+      <c r="Y63" s="7"/>
+      <c r="Z63" s="7"/>
+      <c r="AA63" s="7"/>
+      <c r="AB63" s="7"/>
+      <c r="AC63" s="7"/>
+      <c r="AD63" s="7"/>
+      <c r="AE63" s="7"/>
+      <c r="AF63" s="7"/>
+      <c r="AG63" s="7"/>
+      <c r="AH63" s="7"/>
+      <c r="AI63" s="7"/>
+      <c r="AJ63" s="7"/>
+      <c r="AK63" s="7"/>
+      <c r="AL63" s="7"/>
+      <c r="AM63" s="7"/>
+      <c r="AN63" s="7"/>
+      <c r="AO63" s="7"/>
+      <c r="AP63" s="7"/>
+      <c r="AQ63" s="7"/>
+      <c r="AR63" s="7"/>
+      <c r="AS63" s="7"/>
+      <c r="AT63" s="7"/>
+      <c r="AU63" s="7"/>
+      <c r="AV63" s="7"/>
+      <c r="AW63" s="7"/>
+      <c r="AX63" s="7"/>
+      <c r="AY63" s="7"/>
+      <c r="AZ63" s="7"/>
+      <c r="BA63" s="7"/>
+      <c r="BB63" s="7"/>
+      <c r="BC63" s="7"/>
+      <c r="BD63" s="7"/>
+      <c r="BE63" s="7"/>
+      <c r="BF63" s="7"/>
+      <c r="BG63" s="7"/>
+      <c r="BH63" s="7"/>
+      <c r="BI63" s="7"/>
+      <c r="BJ63" s="7"/>
+      <c r="BK63" s="7"/>
+      <c r="BL63" s="7"/>
+      <c r="BM63" s="7"/>
+      <c r="BN63" s="7"/>
+      <c r="BO63" s="7"/>
+      <c r="BP63" s="7"/>
+      <c r="BQ63" s="7"/>
+      <c r="BR63" s="7"/>
+      <c r="BS63" s="7"/>
+      <c r="BT63" s="7"/>
+      <c r="BU63" s="7"/>
+      <c r="BV63" s="7"/>
+      <c r="BW63" s="7"/>
+      <c r="BX63" s="7"/>
+      <c r="BY63" s="7"/>
+      <c r="BZ63" s="7"/>
+      <c r="CA63" s="7"/>
+      <c r="CB63" s="7"/>
+      <c r="CC63" s="7"/>
+      <c r="CD63" s="7"/>
+      <c r="CE63" s="7"/>
+      <c r="CF63" s="7"/>
+      <c r="CG63" s="7"/>
+      <c r="CH63" s="7"/>
+      <c r="CI63" s="7"/>
+      <c r="CJ63" s="7"/>
+      <c r="CK63" s="7"/>
+      <c r="CL63" s="7"/>
+      <c r="CM63" s="7"/>
+      <c r="CN63" s="7"/>
+      <c r="CO63" s="7"/>
+      <c r="CP63" s="7"/>
+      <c r="CQ63" s="7"/>
+      <c r="CR63" s="7"/>
+      <c r="CS63" s="7"/>
+      <c r="CT63" s="7"/>
+      <c r="CU63" s="7"/>
+      <c r="CV63" s="7"/>
+      <c r="CW63" s="7"/>
+      <c r="CX63" s="7"/>
+      <c r="CY63" s="7"/>
+      <c r="CZ63" s="7"/>
+      <c r="DA63" s="7"/>
+      <c r="DB63" s="7"/>
+      <c r="DC63" s="7"/>
+      <c r="DD63" s="7"/>
+      <c r="DE63" s="7"/>
+      <c r="DF63" s="7"/>
+      <c r="DG63" s="7"/>
+      <c r="DH63" s="7"/>
+      <c r="DI63" s="7"/>
+      <c r="DJ63" s="7"/>
+      <c r="DK63" s="7"/>
+      <c r="DL63" s="7"/>
+      <c r="DM63" s="7"/>
+      <c r="DN63" s="7"/>
+      <c r="DO63" s="7"/>
+      <c r="DP63" s="7"/>
+      <c r="DQ63" s="7"/>
+      <c r="DR63" s="7"/>
+      <c r="DS63" s="7"/>
+      <c r="DT63" s="7"/>
+      <c r="DU63" s="7"/>
+      <c r="DV63" s="7"/>
+      <c r="DW63" s="7"/>
+      <c r="DX63" s="7"/>
+      <c r="DY63" s="7"/>
+      <c r="DZ63" s="7"/>
+      <c r="EA63" s="7"/>
+      <c r="EB63" s="7"/>
+      <c r="EC63" s="7"/>
+      <c r="ED63" s="7"/>
+      <c r="EE63" s="7"/>
+      <c r="EF63" s="7"/>
+      <c r="EG63" s="7"/>
+      <c r="EH63" s="7"/>
+      <c r="EI63" s="7"/>
+      <c r="EJ63" s="7"/>
+      <c r="EK63" s="7"/>
+      <c r="EL63" s="7"/>
+      <c r="EM63" s="7"/>
+      <c r="EN63" s="7"/>
+      <c r="EO63" s="7"/>
+      <c r="EP63" s="7"/>
+      <c r="EQ63" s="7"/>
+      <c r="ER63" s="7"/>
+      <c r="ES63" s="7"/>
+      <c r="ET63" s="7"/>
+      <c r="EU63" s="7"/>
+      <c r="EV63" s="7"/>
+      <c r="EW63" s="7"/>
+      <c r="EX63" s="7"/>
+      <c r="EY63" s="7"/>
+      <c r="EZ63" s="7"/>
+      <c r="FA63" s="7"/>
+      <c r="FB63" s="7"/>
+      <c r="FC63" s="7"/>
+      <c r="FD63" s="7"/>
+      <c r="FE63" s="7"/>
+      <c r="FF63" s="7"/>
+      <c r="FG63" s="7"/>
+      <c r="FH63" s="7"/>
+      <c r="FI63" s="7"/>
+      <c r="FJ63" s="7"/>
+      <c r="FK63" s="7"/>
+      <c r="FL63" s="7"/>
+      <c r="FM63" s="7"/>
+      <c r="FN63" s="7"/>
+      <c r="FO63" s="7"/>
+      <c r="FP63" s="7"/>
+      <c r="FQ63" s="7"/>
+      <c r="FR63" s="7"/>
+      <c r="FS63" s="7"/>
+      <c r="FT63" s="7"/>
+      <c r="FU63" s="7"/>
+      <c r="FV63" s="7"/>
+      <c r="FW63" s="7"/>
+      <c r="FX63" s="7"/>
+      <c r="FY63" s="7"/>
+      <c r="FZ63" s="7"/>
+      <c r="GA63" s="7"/>
+      <c r="GB63" s="7"/>
+      <c r="GC63" s="7"/>
+      <c r="GD63" s="7"/>
+      <c r="GE63" s="7"/>
+      <c r="GF63" s="7"/>
+      <c r="GG63" s="7"/>
+      <c r="GH63" s="7"/>
+      <c r="GI63" s="7"/>
+      <c r="GJ63" s="7"/>
+      <c r="GK63" s="7"/>
+      <c r="GL63" s="7"/>
+      <c r="GM63" s="7"/>
+      <c r="GN63" s="7"/>
+      <c r="GO63" s="7"/>
+      <c r="GP63" s="7"/>
+      <c r="GQ63" s="7"/>
+      <c r="GR63" s="7"/>
+      <c r="GS63" s="7"/>
+      <c r="GT63" s="7"/>
+      <c r="GU63" s="7"/>
+      <c r="GV63" s="7"/>
+      <c r="GW63" s="7"/>
+      <c r="GX63" s="7"/>
+      <c r="GY63" s="7"/>
+      <c r="GZ63" s="7"/>
+      <c r="HA63" s="7"/>
+      <c r="HB63" s="7"/>
+      <c r="HC63" s="7"/>
+      <c r="HD63" s="7"/>
+      <c r="HE63" s="7"/>
+      <c r="HF63" s="7"/>
+      <c r="HG63" s="7"/>
+      <c r="HH63" s="7"/>
+      <c r="HI63" s="7"/>
+      <c r="HJ63" s="7"/>
+      <c r="HK63" s="7"/>
+      <c r="HL63" s="7"/>
+      <c r="HM63" s="7"/>
+      <c r="HN63" s="7"/>
+      <c r="HO63" s="7"/>
+      <c r="HP63" s="7"/>
+      <c r="HQ63" s="7"/>
+      <c r="HR63" s="7"/>
+      <c r="HS63" s="7"/>
+      <c r="HT63" s="7"/>
+      <c r="HU63" s="7"/>
+      <c r="HV63" s="7"/>
+      <c r="HW63" s="7"/>
+      <c r="HX63" s="7"/>
+      <c r="HY63" s="7"/>
+      <c r="HZ63" s="7"/>
+      <c r="IA63" s="7"/>
+      <c r="IB63" s="7"/>
+      <c r="IC63" s="7"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="36"/>
@@ -13693,7 +13891,7 @@
       </c>
       <c r="E64" s="36"/>
     </row>
-    <row r="65" s="34" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="32"/>
       <c r="B65" s="31" t="n">
         <f aca="false">B64+1</f>
@@ -13706,240 +13904,8 @@
         <v>37</v>
       </c>
       <c r="E65" s="32"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="7"/>
-      <c r="K65" s="7"/>
-      <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
-      <c r="N65" s="7"/>
-      <c r="O65" s="7"/>
-      <c r="P65" s="7"/>
-      <c r="Q65" s="7"/>
-      <c r="R65" s="7"/>
-      <c r="S65" s="7"/>
-      <c r="T65" s="7"/>
-      <c r="U65" s="7"/>
-      <c r="V65" s="7"/>
-      <c r="W65" s="7"/>
-      <c r="X65" s="7"/>
-      <c r="Y65" s="7"/>
-      <c r="Z65" s="7"/>
-      <c r="AA65" s="7"/>
-      <c r="AB65" s="7"/>
-      <c r="AC65" s="7"/>
-      <c r="AD65" s="7"/>
-      <c r="AE65" s="7"/>
-      <c r="AF65" s="7"/>
-      <c r="AG65" s="7"/>
-      <c r="AH65" s="7"/>
-      <c r="AI65" s="7"/>
-      <c r="AJ65" s="7"/>
-      <c r="AK65" s="7"/>
-      <c r="AL65" s="7"/>
-      <c r="AM65" s="7"/>
-      <c r="AN65" s="7"/>
-      <c r="AO65" s="7"/>
-      <c r="AP65" s="7"/>
-      <c r="AQ65" s="7"/>
-      <c r="AR65" s="7"/>
-      <c r="AS65" s="7"/>
-      <c r="AT65" s="7"/>
-      <c r="AU65" s="7"/>
-      <c r="AV65" s="7"/>
-      <c r="AW65" s="7"/>
-      <c r="AX65" s="7"/>
-      <c r="AY65" s="7"/>
-      <c r="AZ65" s="7"/>
-      <c r="BA65" s="7"/>
-      <c r="BB65" s="7"/>
-      <c r="BC65" s="7"/>
-      <c r="BD65" s="7"/>
-      <c r="BE65" s="7"/>
-      <c r="BF65" s="7"/>
-      <c r="BG65" s="7"/>
-      <c r="BH65" s="7"/>
-      <c r="BI65" s="7"/>
-      <c r="BJ65" s="7"/>
-      <c r="BK65" s="7"/>
-      <c r="BL65" s="7"/>
-      <c r="BM65" s="7"/>
-      <c r="BN65" s="7"/>
-      <c r="BO65" s="7"/>
-      <c r="BP65" s="7"/>
-      <c r="BQ65" s="7"/>
-      <c r="BR65" s="7"/>
-      <c r="BS65" s="7"/>
-      <c r="BT65" s="7"/>
-      <c r="BU65" s="7"/>
-      <c r="BV65" s="7"/>
-      <c r="BW65" s="7"/>
-      <c r="BX65" s="7"/>
-      <c r="BY65" s="7"/>
-      <c r="BZ65" s="7"/>
-      <c r="CA65" s="7"/>
-      <c r="CB65" s="7"/>
-      <c r="CC65" s="7"/>
-      <c r="CD65" s="7"/>
-      <c r="CE65" s="7"/>
-      <c r="CF65" s="7"/>
-      <c r="CG65" s="7"/>
-      <c r="CH65" s="7"/>
-      <c r="CI65" s="7"/>
-      <c r="CJ65" s="7"/>
-      <c r="CK65" s="7"/>
-      <c r="CL65" s="7"/>
-      <c r="CM65" s="7"/>
-      <c r="CN65" s="7"/>
-      <c r="CO65" s="7"/>
-      <c r="CP65" s="7"/>
-      <c r="CQ65" s="7"/>
-      <c r="CR65" s="7"/>
-      <c r="CS65" s="7"/>
-      <c r="CT65" s="7"/>
-      <c r="CU65" s="7"/>
-      <c r="CV65" s="7"/>
-      <c r="CW65" s="7"/>
-      <c r="CX65" s="7"/>
-      <c r="CY65" s="7"/>
-      <c r="CZ65" s="7"/>
-      <c r="DA65" s="7"/>
-      <c r="DB65" s="7"/>
-      <c r="DC65" s="7"/>
-      <c r="DD65" s="7"/>
-      <c r="DE65" s="7"/>
-      <c r="DF65" s="7"/>
-      <c r="DG65" s="7"/>
-      <c r="DH65" s="7"/>
-      <c r="DI65" s="7"/>
-      <c r="DJ65" s="7"/>
-      <c r="DK65" s="7"/>
-      <c r="DL65" s="7"/>
-      <c r="DM65" s="7"/>
-      <c r="DN65" s="7"/>
-      <c r="DO65" s="7"/>
-      <c r="DP65" s="7"/>
-      <c r="DQ65" s="7"/>
-      <c r="DR65" s="7"/>
-      <c r="DS65" s="7"/>
-      <c r="DT65" s="7"/>
-      <c r="DU65" s="7"/>
-      <c r="DV65" s="7"/>
-      <c r="DW65" s="7"/>
-      <c r="DX65" s="7"/>
-      <c r="DY65" s="7"/>
-      <c r="DZ65" s="7"/>
-      <c r="EA65" s="7"/>
-      <c r="EB65" s="7"/>
-      <c r="EC65" s="7"/>
-      <c r="ED65" s="7"/>
-      <c r="EE65" s="7"/>
-      <c r="EF65" s="7"/>
-      <c r="EG65" s="7"/>
-      <c r="EH65" s="7"/>
-      <c r="EI65" s="7"/>
-      <c r="EJ65" s="7"/>
-      <c r="EK65" s="7"/>
-      <c r="EL65" s="7"/>
-      <c r="EM65" s="7"/>
-      <c r="EN65" s="7"/>
-      <c r="EO65" s="7"/>
-      <c r="EP65" s="7"/>
-      <c r="EQ65" s="7"/>
-      <c r="ER65" s="7"/>
-      <c r="ES65" s="7"/>
-      <c r="ET65" s="7"/>
-      <c r="EU65" s="7"/>
-      <c r="EV65" s="7"/>
-      <c r="EW65" s="7"/>
-      <c r="EX65" s="7"/>
-      <c r="EY65" s="7"/>
-      <c r="EZ65" s="7"/>
-      <c r="FA65" s="7"/>
-      <c r="FB65" s="7"/>
-      <c r="FC65" s="7"/>
-      <c r="FD65" s="7"/>
-      <c r="FE65" s="7"/>
-      <c r="FF65" s="7"/>
-      <c r="FG65" s="7"/>
-      <c r="FH65" s="7"/>
-      <c r="FI65" s="7"/>
-      <c r="FJ65" s="7"/>
-      <c r="FK65" s="7"/>
-      <c r="FL65" s="7"/>
-      <c r="FM65" s="7"/>
-      <c r="FN65" s="7"/>
-      <c r="FO65" s="7"/>
-      <c r="FP65" s="7"/>
-      <c r="FQ65" s="7"/>
-      <c r="FR65" s="7"/>
-      <c r="FS65" s="7"/>
-      <c r="FT65" s="7"/>
-      <c r="FU65" s="7"/>
-      <c r="FV65" s="7"/>
-      <c r="FW65" s="7"/>
-      <c r="FX65" s="7"/>
-      <c r="FY65" s="7"/>
-      <c r="FZ65" s="7"/>
-      <c r="GA65" s="7"/>
-      <c r="GB65" s="7"/>
-      <c r="GC65" s="7"/>
-      <c r="GD65" s="7"/>
-      <c r="GE65" s="7"/>
-      <c r="GF65" s="7"/>
-      <c r="GG65" s="7"/>
-      <c r="GH65" s="7"/>
-      <c r="GI65" s="7"/>
-      <c r="GJ65" s="7"/>
-      <c r="GK65" s="7"/>
-      <c r="GL65" s="7"/>
-      <c r="GM65" s="7"/>
-      <c r="GN65" s="7"/>
-      <c r="GO65" s="7"/>
-      <c r="GP65" s="7"/>
-      <c r="GQ65" s="7"/>
-      <c r="GR65" s="7"/>
-      <c r="GS65" s="7"/>
-      <c r="GT65" s="7"/>
-      <c r="GU65" s="7"/>
-      <c r="GV65" s="7"/>
-      <c r="GW65" s="7"/>
-      <c r="GX65" s="7"/>
-      <c r="GY65" s="7"/>
-      <c r="GZ65" s="7"/>
-      <c r="HA65" s="7"/>
-      <c r="HB65" s="7"/>
-      <c r="HC65" s="7"/>
-      <c r="HD65" s="7"/>
-      <c r="HE65" s="7"/>
-      <c r="HF65" s="7"/>
-      <c r="HG65" s="7"/>
-      <c r="HH65" s="7"/>
-      <c r="HI65" s="7"/>
-      <c r="HJ65" s="7"/>
-      <c r="HK65" s="7"/>
-      <c r="HL65" s="7"/>
-      <c r="HM65" s="7"/>
-      <c r="HN65" s="7"/>
-      <c r="HO65" s="7"/>
-      <c r="HP65" s="7"/>
-      <c r="HQ65" s="7"/>
-      <c r="HR65" s="7"/>
-      <c r="HS65" s="7"/>
-      <c r="HT65" s="7"/>
-      <c r="HU65" s="7"/>
-      <c r="HV65" s="7"/>
-      <c r="HW65" s="7"/>
-      <c r="HX65" s="7"/>
-      <c r="HY65" s="7"/>
-      <c r="HZ65" s="7"/>
-      <c r="IA65" s="7"/>
-      <c r="IB65" s="7"/>
-      <c r="IC65" s="7"/>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="66" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="32"/>
       <c r="B66" s="31" t="n">
         <f aca="false">B65+1</f>
@@ -13952,8 +13918,240 @@
         <v>38</v>
       </c>
       <c r="E66" s="32"/>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="7"/>
+      <c r="K66" s="7"/>
+      <c r="L66" s="7"/>
+      <c r="M66" s="7"/>
+      <c r="N66" s="7"/>
+      <c r="O66" s="7"/>
+      <c r="P66" s="7"/>
+      <c r="Q66" s="7"/>
+      <c r="R66" s="7"/>
+      <c r="S66" s="7"/>
+      <c r="T66" s="7"/>
+      <c r="U66" s="7"/>
+      <c r="V66" s="7"/>
+      <c r="W66" s="7"/>
+      <c r="X66" s="7"/>
+      <c r="Y66" s="7"/>
+      <c r="Z66" s="7"/>
+      <c r="AA66" s="7"/>
+      <c r="AB66" s="7"/>
+      <c r="AC66" s="7"/>
+      <c r="AD66" s="7"/>
+      <c r="AE66" s="7"/>
+      <c r="AF66" s="7"/>
+      <c r="AG66" s="7"/>
+      <c r="AH66" s="7"/>
+      <c r="AI66" s="7"/>
+      <c r="AJ66" s="7"/>
+      <c r="AK66" s="7"/>
+      <c r="AL66" s="7"/>
+      <c r="AM66" s="7"/>
+      <c r="AN66" s="7"/>
+      <c r="AO66" s="7"/>
+      <c r="AP66" s="7"/>
+      <c r="AQ66" s="7"/>
+      <c r="AR66" s="7"/>
+      <c r="AS66" s="7"/>
+      <c r="AT66" s="7"/>
+      <c r="AU66" s="7"/>
+      <c r="AV66" s="7"/>
+      <c r="AW66" s="7"/>
+      <c r="AX66" s="7"/>
+      <c r="AY66" s="7"/>
+      <c r="AZ66" s="7"/>
+      <c r="BA66" s="7"/>
+      <c r="BB66" s="7"/>
+      <c r="BC66" s="7"/>
+      <c r="BD66" s="7"/>
+      <c r="BE66" s="7"/>
+      <c r="BF66" s="7"/>
+      <c r="BG66" s="7"/>
+      <c r="BH66" s="7"/>
+      <c r="BI66" s="7"/>
+      <c r="BJ66" s="7"/>
+      <c r="BK66" s="7"/>
+      <c r="BL66" s="7"/>
+      <c r="BM66" s="7"/>
+      <c r="BN66" s="7"/>
+      <c r="BO66" s="7"/>
+      <c r="BP66" s="7"/>
+      <c r="BQ66" s="7"/>
+      <c r="BR66" s="7"/>
+      <c r="BS66" s="7"/>
+      <c r="BT66" s="7"/>
+      <c r="BU66" s="7"/>
+      <c r="BV66" s="7"/>
+      <c r="BW66" s="7"/>
+      <c r="BX66" s="7"/>
+      <c r="BY66" s="7"/>
+      <c r="BZ66" s="7"/>
+      <c r="CA66" s="7"/>
+      <c r="CB66" s="7"/>
+      <c r="CC66" s="7"/>
+      <c r="CD66" s="7"/>
+      <c r="CE66" s="7"/>
+      <c r="CF66" s="7"/>
+      <c r="CG66" s="7"/>
+      <c r="CH66" s="7"/>
+      <c r="CI66" s="7"/>
+      <c r="CJ66" s="7"/>
+      <c r="CK66" s="7"/>
+      <c r="CL66" s="7"/>
+      <c r="CM66" s="7"/>
+      <c r="CN66" s="7"/>
+      <c r="CO66" s="7"/>
+      <c r="CP66" s="7"/>
+      <c r="CQ66" s="7"/>
+      <c r="CR66" s="7"/>
+      <c r="CS66" s="7"/>
+      <c r="CT66" s="7"/>
+      <c r="CU66" s="7"/>
+      <c r="CV66" s="7"/>
+      <c r="CW66" s="7"/>
+      <c r="CX66" s="7"/>
+      <c r="CY66" s="7"/>
+      <c r="CZ66" s="7"/>
+      <c r="DA66" s="7"/>
+      <c r="DB66" s="7"/>
+      <c r="DC66" s="7"/>
+      <c r="DD66" s="7"/>
+      <c r="DE66" s="7"/>
+      <c r="DF66" s="7"/>
+      <c r="DG66" s="7"/>
+      <c r="DH66" s="7"/>
+      <c r="DI66" s="7"/>
+      <c r="DJ66" s="7"/>
+      <c r="DK66" s="7"/>
+      <c r="DL66" s="7"/>
+      <c r="DM66" s="7"/>
+      <c r="DN66" s="7"/>
+      <c r="DO66" s="7"/>
+      <c r="DP66" s="7"/>
+      <c r="DQ66" s="7"/>
+      <c r="DR66" s="7"/>
+      <c r="DS66" s="7"/>
+      <c r="DT66" s="7"/>
+      <c r="DU66" s="7"/>
+      <c r="DV66" s="7"/>
+      <c r="DW66" s="7"/>
+      <c r="DX66" s="7"/>
+      <c r="DY66" s="7"/>
+      <c r="DZ66" s="7"/>
+      <c r="EA66" s="7"/>
+      <c r="EB66" s="7"/>
+      <c r="EC66" s="7"/>
+      <c r="ED66" s="7"/>
+      <c r="EE66" s="7"/>
+      <c r="EF66" s="7"/>
+      <c r="EG66" s="7"/>
+      <c r="EH66" s="7"/>
+      <c r="EI66" s="7"/>
+      <c r="EJ66" s="7"/>
+      <c r="EK66" s="7"/>
+      <c r="EL66" s="7"/>
+      <c r="EM66" s="7"/>
+      <c r="EN66" s="7"/>
+      <c r="EO66" s="7"/>
+      <c r="EP66" s="7"/>
+      <c r="EQ66" s="7"/>
+      <c r="ER66" s="7"/>
+      <c r="ES66" s="7"/>
+      <c r="ET66" s="7"/>
+      <c r="EU66" s="7"/>
+      <c r="EV66" s="7"/>
+      <c r="EW66" s="7"/>
+      <c r="EX66" s="7"/>
+      <c r="EY66" s="7"/>
+      <c r="EZ66" s="7"/>
+      <c r="FA66" s="7"/>
+      <c r="FB66" s="7"/>
+      <c r="FC66" s="7"/>
+      <c r="FD66" s="7"/>
+      <c r="FE66" s="7"/>
+      <c r="FF66" s="7"/>
+      <c r="FG66" s="7"/>
+      <c r="FH66" s="7"/>
+      <c r="FI66" s="7"/>
+      <c r="FJ66" s="7"/>
+      <c r="FK66" s="7"/>
+      <c r="FL66" s="7"/>
+      <c r="FM66" s="7"/>
+      <c r="FN66" s="7"/>
+      <c r="FO66" s="7"/>
+      <c r="FP66" s="7"/>
+      <c r="FQ66" s="7"/>
+      <c r="FR66" s="7"/>
+      <c r="FS66" s="7"/>
+      <c r="FT66" s="7"/>
+      <c r="FU66" s="7"/>
+      <c r="FV66" s="7"/>
+      <c r="FW66" s="7"/>
+      <c r="FX66" s="7"/>
+      <c r="FY66" s="7"/>
+      <c r="FZ66" s="7"/>
+      <c r="GA66" s="7"/>
+      <c r="GB66" s="7"/>
+      <c r="GC66" s="7"/>
+      <c r="GD66" s="7"/>
+      <c r="GE66" s="7"/>
+      <c r="GF66" s="7"/>
+      <c r="GG66" s="7"/>
+      <c r="GH66" s="7"/>
+      <c r="GI66" s="7"/>
+      <c r="GJ66" s="7"/>
+      <c r="GK66" s="7"/>
+      <c r="GL66" s="7"/>
+      <c r="GM66" s="7"/>
+      <c r="GN66" s="7"/>
+      <c r="GO66" s="7"/>
+      <c r="GP66" s="7"/>
+      <c r="GQ66" s="7"/>
+      <c r="GR66" s="7"/>
+      <c r="GS66" s="7"/>
+      <c r="GT66" s="7"/>
+      <c r="GU66" s="7"/>
+      <c r="GV66" s="7"/>
+      <c r="GW66" s="7"/>
+      <c r="GX66" s="7"/>
+      <c r="GY66" s="7"/>
+      <c r="GZ66" s="7"/>
+      <c r="HA66" s="7"/>
+      <c r="HB66" s="7"/>
+      <c r="HC66" s="7"/>
+      <c r="HD66" s="7"/>
+      <c r="HE66" s="7"/>
+      <c r="HF66" s="7"/>
+      <c r="HG66" s="7"/>
+      <c r="HH66" s="7"/>
+      <c r="HI66" s="7"/>
+      <c r="HJ66" s="7"/>
+      <c r="HK66" s="7"/>
+      <c r="HL66" s="7"/>
+      <c r="HM66" s="7"/>
+      <c r="HN66" s="7"/>
+      <c r="HO66" s="7"/>
+      <c r="HP66" s="7"/>
+      <c r="HQ66" s="7"/>
+      <c r="HR66" s="7"/>
+      <c r="HS66" s="7"/>
+      <c r="HT66" s="7"/>
+      <c r="HU66" s="7"/>
+      <c r="HV66" s="7"/>
+      <c r="HW66" s="7"/>
+      <c r="HX66" s="7"/>
+      <c r="HY66" s="7"/>
+      <c r="HZ66" s="7"/>
+      <c r="IA66" s="7"/>
+      <c r="IB66" s="7"/>
+      <c r="IC66" s="7"/>
+    </row>
+    <row r="67" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="36"/>
       <c r="B67" s="35" t="n">
         <f aca="false">B66+1</f>
@@ -13966,8 +14164,240 @@
         <v>39</v>
       </c>
       <c r="E67" s="36"/>
-    </row>
-    <row r="68" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+      <c r="M67" s="7"/>
+      <c r="N67" s="7"/>
+      <c r="O67" s="7"/>
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
+      <c r="R67" s="7"/>
+      <c r="S67" s="7"/>
+      <c r="T67" s="7"/>
+      <c r="U67" s="7"/>
+      <c r="V67" s="7"/>
+      <c r="W67" s="7"/>
+      <c r="X67" s="7"/>
+      <c r="Y67" s="7"/>
+      <c r="Z67" s="7"/>
+      <c r="AA67" s="7"/>
+      <c r="AB67" s="7"/>
+      <c r="AC67" s="7"/>
+      <c r="AD67" s="7"/>
+      <c r="AE67" s="7"/>
+      <c r="AF67" s="7"/>
+      <c r="AG67" s="7"/>
+      <c r="AH67" s="7"/>
+      <c r="AI67" s="7"/>
+      <c r="AJ67" s="7"/>
+      <c r="AK67" s="7"/>
+      <c r="AL67" s="7"/>
+      <c r="AM67" s="7"/>
+      <c r="AN67" s="7"/>
+      <c r="AO67" s="7"/>
+      <c r="AP67" s="7"/>
+      <c r="AQ67" s="7"/>
+      <c r="AR67" s="7"/>
+      <c r="AS67" s="7"/>
+      <c r="AT67" s="7"/>
+      <c r="AU67" s="7"/>
+      <c r="AV67" s="7"/>
+      <c r="AW67" s="7"/>
+      <c r="AX67" s="7"/>
+      <c r="AY67" s="7"/>
+      <c r="AZ67" s="7"/>
+      <c r="BA67" s="7"/>
+      <c r="BB67" s="7"/>
+      <c r="BC67" s="7"/>
+      <c r="BD67" s="7"/>
+      <c r="BE67" s="7"/>
+      <c r="BF67" s="7"/>
+      <c r="BG67" s="7"/>
+      <c r="BH67" s="7"/>
+      <c r="BI67" s="7"/>
+      <c r="BJ67" s="7"/>
+      <c r="BK67" s="7"/>
+      <c r="BL67" s="7"/>
+      <c r="BM67" s="7"/>
+      <c r="BN67" s="7"/>
+      <c r="BO67" s="7"/>
+      <c r="BP67" s="7"/>
+      <c r="BQ67" s="7"/>
+      <c r="BR67" s="7"/>
+      <c r="BS67" s="7"/>
+      <c r="BT67" s="7"/>
+      <c r="BU67" s="7"/>
+      <c r="BV67" s="7"/>
+      <c r="BW67" s="7"/>
+      <c r="BX67" s="7"/>
+      <c r="BY67" s="7"/>
+      <c r="BZ67" s="7"/>
+      <c r="CA67" s="7"/>
+      <c r="CB67" s="7"/>
+      <c r="CC67" s="7"/>
+      <c r="CD67" s="7"/>
+      <c r="CE67" s="7"/>
+      <c r="CF67" s="7"/>
+      <c r="CG67" s="7"/>
+      <c r="CH67" s="7"/>
+      <c r="CI67" s="7"/>
+      <c r="CJ67" s="7"/>
+      <c r="CK67" s="7"/>
+      <c r="CL67" s="7"/>
+      <c r="CM67" s="7"/>
+      <c r="CN67" s="7"/>
+      <c r="CO67" s="7"/>
+      <c r="CP67" s="7"/>
+      <c r="CQ67" s="7"/>
+      <c r="CR67" s="7"/>
+      <c r="CS67" s="7"/>
+      <c r="CT67" s="7"/>
+      <c r="CU67" s="7"/>
+      <c r="CV67" s="7"/>
+      <c r="CW67" s="7"/>
+      <c r="CX67" s="7"/>
+      <c r="CY67" s="7"/>
+      <c r="CZ67" s="7"/>
+      <c r="DA67" s="7"/>
+      <c r="DB67" s="7"/>
+      <c r="DC67" s="7"/>
+      <c r="DD67" s="7"/>
+      <c r="DE67" s="7"/>
+      <c r="DF67" s="7"/>
+      <c r="DG67" s="7"/>
+      <c r="DH67" s="7"/>
+      <c r="DI67" s="7"/>
+      <c r="DJ67" s="7"/>
+      <c r="DK67" s="7"/>
+      <c r="DL67" s="7"/>
+      <c r="DM67" s="7"/>
+      <c r="DN67" s="7"/>
+      <c r="DO67" s="7"/>
+      <c r="DP67" s="7"/>
+      <c r="DQ67" s="7"/>
+      <c r="DR67" s="7"/>
+      <c r="DS67" s="7"/>
+      <c r="DT67" s="7"/>
+      <c r="DU67" s="7"/>
+      <c r="DV67" s="7"/>
+      <c r="DW67" s="7"/>
+      <c r="DX67" s="7"/>
+      <c r="DY67" s="7"/>
+      <c r="DZ67" s="7"/>
+      <c r="EA67" s="7"/>
+      <c r="EB67" s="7"/>
+      <c r="EC67" s="7"/>
+      <c r="ED67" s="7"/>
+      <c r="EE67" s="7"/>
+      <c r="EF67" s="7"/>
+      <c r="EG67" s="7"/>
+      <c r="EH67" s="7"/>
+      <c r="EI67" s="7"/>
+      <c r="EJ67" s="7"/>
+      <c r="EK67" s="7"/>
+      <c r="EL67" s="7"/>
+      <c r="EM67" s="7"/>
+      <c r="EN67" s="7"/>
+      <c r="EO67" s="7"/>
+      <c r="EP67" s="7"/>
+      <c r="EQ67" s="7"/>
+      <c r="ER67" s="7"/>
+      <c r="ES67" s="7"/>
+      <c r="ET67" s="7"/>
+      <c r="EU67" s="7"/>
+      <c r="EV67" s="7"/>
+      <c r="EW67" s="7"/>
+      <c r="EX67" s="7"/>
+      <c r="EY67" s="7"/>
+      <c r="EZ67" s="7"/>
+      <c r="FA67" s="7"/>
+      <c r="FB67" s="7"/>
+      <c r="FC67" s="7"/>
+      <c r="FD67" s="7"/>
+      <c r="FE67" s="7"/>
+      <c r="FF67" s="7"/>
+      <c r="FG67" s="7"/>
+      <c r="FH67" s="7"/>
+      <c r="FI67" s="7"/>
+      <c r="FJ67" s="7"/>
+      <c r="FK67" s="7"/>
+      <c r="FL67" s="7"/>
+      <c r="FM67" s="7"/>
+      <c r="FN67" s="7"/>
+      <c r="FO67" s="7"/>
+      <c r="FP67" s="7"/>
+      <c r="FQ67" s="7"/>
+      <c r="FR67" s="7"/>
+      <c r="FS67" s="7"/>
+      <c r="FT67" s="7"/>
+      <c r="FU67" s="7"/>
+      <c r="FV67" s="7"/>
+      <c r="FW67" s="7"/>
+      <c r="FX67" s="7"/>
+      <c r="FY67" s="7"/>
+      <c r="FZ67" s="7"/>
+      <c r="GA67" s="7"/>
+      <c r="GB67" s="7"/>
+      <c r="GC67" s="7"/>
+      <c r="GD67" s="7"/>
+      <c r="GE67" s="7"/>
+      <c r="GF67" s="7"/>
+      <c r="GG67" s="7"/>
+      <c r="GH67" s="7"/>
+      <c r="GI67" s="7"/>
+      <c r="GJ67" s="7"/>
+      <c r="GK67" s="7"/>
+      <c r="GL67" s="7"/>
+      <c r="GM67" s="7"/>
+      <c r="GN67" s="7"/>
+      <c r="GO67" s="7"/>
+      <c r="GP67" s="7"/>
+      <c r="GQ67" s="7"/>
+      <c r="GR67" s="7"/>
+      <c r="GS67" s="7"/>
+      <c r="GT67" s="7"/>
+      <c r="GU67" s="7"/>
+      <c r="GV67" s="7"/>
+      <c r="GW67" s="7"/>
+      <c r="GX67" s="7"/>
+      <c r="GY67" s="7"/>
+      <c r="GZ67" s="7"/>
+      <c r="HA67" s="7"/>
+      <c r="HB67" s="7"/>
+      <c r="HC67" s="7"/>
+      <c r="HD67" s="7"/>
+      <c r="HE67" s="7"/>
+      <c r="HF67" s="7"/>
+      <c r="HG67" s="7"/>
+      <c r="HH67" s="7"/>
+      <c r="HI67" s="7"/>
+      <c r="HJ67" s="7"/>
+      <c r="HK67" s="7"/>
+      <c r="HL67" s="7"/>
+      <c r="HM67" s="7"/>
+      <c r="HN67" s="7"/>
+      <c r="HO67" s="7"/>
+      <c r="HP67" s="7"/>
+      <c r="HQ67" s="7"/>
+      <c r="HR67" s="7"/>
+      <c r="HS67" s="7"/>
+      <c r="HT67" s="7"/>
+      <c r="HU67" s="7"/>
+      <c r="HV67" s="7"/>
+      <c r="HW67" s="7"/>
+      <c r="HX67" s="7"/>
+      <c r="HY67" s="7"/>
+      <c r="HZ67" s="7"/>
+      <c r="IA67" s="7"/>
+      <c r="IB67" s="7"/>
+      <c r="IC67" s="7"/>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="36"/>
       <c r="B68" s="35" t="n">
         <f aca="false">B67+1</f>
@@ -13980,240 +14410,8 @@
         <v>40</v>
       </c>
       <c r="E68" s="36"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
-      <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="7"/>
-      <c r="O68" s="7"/>
-      <c r="P68" s="7"/>
-      <c r="Q68" s="7"/>
-      <c r="R68" s="7"/>
-      <c r="S68" s="7"/>
-      <c r="T68" s="7"/>
-      <c r="U68" s="7"/>
-      <c r="V68" s="7"/>
-      <c r="W68" s="7"/>
-      <c r="X68" s="7"/>
-      <c r="Y68" s="7"/>
-      <c r="Z68" s="7"/>
-      <c r="AA68" s="7"/>
-      <c r="AB68" s="7"/>
-      <c r="AC68" s="7"/>
-      <c r="AD68" s="7"/>
-      <c r="AE68" s="7"/>
-      <c r="AF68" s="7"/>
-      <c r="AG68" s="7"/>
-      <c r="AH68" s="7"/>
-      <c r="AI68" s="7"/>
-      <c r="AJ68" s="7"/>
-      <c r="AK68" s="7"/>
-      <c r="AL68" s="7"/>
-      <c r="AM68" s="7"/>
-      <c r="AN68" s="7"/>
-      <c r="AO68" s="7"/>
-      <c r="AP68" s="7"/>
-      <c r="AQ68" s="7"/>
-      <c r="AR68" s="7"/>
-      <c r="AS68" s="7"/>
-      <c r="AT68" s="7"/>
-      <c r="AU68" s="7"/>
-      <c r="AV68" s="7"/>
-      <c r="AW68" s="7"/>
-      <c r="AX68" s="7"/>
-      <c r="AY68" s="7"/>
-      <c r="AZ68" s="7"/>
-      <c r="BA68" s="7"/>
-      <c r="BB68" s="7"/>
-      <c r="BC68" s="7"/>
-      <c r="BD68" s="7"/>
-      <c r="BE68" s="7"/>
-      <c r="BF68" s="7"/>
-      <c r="BG68" s="7"/>
-      <c r="BH68" s="7"/>
-      <c r="BI68" s="7"/>
-      <c r="BJ68" s="7"/>
-      <c r="BK68" s="7"/>
-      <c r="BL68" s="7"/>
-      <c r="BM68" s="7"/>
-      <c r="BN68" s="7"/>
-      <c r="BO68" s="7"/>
-      <c r="BP68" s="7"/>
-      <c r="BQ68" s="7"/>
-      <c r="BR68" s="7"/>
-      <c r="BS68" s="7"/>
-      <c r="BT68" s="7"/>
-      <c r="BU68" s="7"/>
-      <c r="BV68" s="7"/>
-      <c r="BW68" s="7"/>
-      <c r="BX68" s="7"/>
-      <c r="BY68" s="7"/>
-      <c r="BZ68" s="7"/>
-      <c r="CA68" s="7"/>
-      <c r="CB68" s="7"/>
-      <c r="CC68" s="7"/>
-      <c r="CD68" s="7"/>
-      <c r="CE68" s="7"/>
-      <c r="CF68" s="7"/>
-      <c r="CG68" s="7"/>
-      <c r="CH68" s="7"/>
-      <c r="CI68" s="7"/>
-      <c r="CJ68" s="7"/>
-      <c r="CK68" s="7"/>
-      <c r="CL68" s="7"/>
-      <c r="CM68" s="7"/>
-      <c r="CN68" s="7"/>
-      <c r="CO68" s="7"/>
-      <c r="CP68" s="7"/>
-      <c r="CQ68" s="7"/>
-      <c r="CR68" s="7"/>
-      <c r="CS68" s="7"/>
-      <c r="CT68" s="7"/>
-      <c r="CU68" s="7"/>
-      <c r="CV68" s="7"/>
-      <c r="CW68" s="7"/>
-      <c r="CX68" s="7"/>
-      <c r="CY68" s="7"/>
-      <c r="CZ68" s="7"/>
-      <c r="DA68" s="7"/>
-      <c r="DB68" s="7"/>
-      <c r="DC68" s="7"/>
-      <c r="DD68" s="7"/>
-      <c r="DE68" s="7"/>
-      <c r="DF68" s="7"/>
-      <c r="DG68" s="7"/>
-      <c r="DH68" s="7"/>
-      <c r="DI68" s="7"/>
-      <c r="DJ68" s="7"/>
-      <c r="DK68" s="7"/>
-      <c r="DL68" s="7"/>
-      <c r="DM68" s="7"/>
-      <c r="DN68" s="7"/>
-      <c r="DO68" s="7"/>
-      <c r="DP68" s="7"/>
-      <c r="DQ68" s="7"/>
-      <c r="DR68" s="7"/>
-      <c r="DS68" s="7"/>
-      <c r="DT68" s="7"/>
-      <c r="DU68" s="7"/>
-      <c r="DV68" s="7"/>
-      <c r="DW68" s="7"/>
-      <c r="DX68" s="7"/>
-      <c r="DY68" s="7"/>
-      <c r="DZ68" s="7"/>
-      <c r="EA68" s="7"/>
-      <c r="EB68" s="7"/>
-      <c r="EC68" s="7"/>
-      <c r="ED68" s="7"/>
-      <c r="EE68" s="7"/>
-      <c r="EF68" s="7"/>
-      <c r="EG68" s="7"/>
-      <c r="EH68" s="7"/>
-      <c r="EI68" s="7"/>
-      <c r="EJ68" s="7"/>
-      <c r="EK68" s="7"/>
-      <c r="EL68" s="7"/>
-      <c r="EM68" s="7"/>
-      <c r="EN68" s="7"/>
-      <c r="EO68" s="7"/>
-      <c r="EP68" s="7"/>
-      <c r="EQ68" s="7"/>
-      <c r="ER68" s="7"/>
-      <c r="ES68" s="7"/>
-      <c r="ET68" s="7"/>
-      <c r="EU68" s="7"/>
-      <c r="EV68" s="7"/>
-      <c r="EW68" s="7"/>
-      <c r="EX68" s="7"/>
-      <c r="EY68" s="7"/>
-      <c r="EZ68" s="7"/>
-      <c r="FA68" s="7"/>
-      <c r="FB68" s="7"/>
-      <c r="FC68" s="7"/>
-      <c r="FD68" s="7"/>
-      <c r="FE68" s="7"/>
-      <c r="FF68" s="7"/>
-      <c r="FG68" s="7"/>
-      <c r="FH68" s="7"/>
-      <c r="FI68" s="7"/>
-      <c r="FJ68" s="7"/>
-      <c r="FK68" s="7"/>
-      <c r="FL68" s="7"/>
-      <c r="FM68" s="7"/>
-      <c r="FN68" s="7"/>
-      <c r="FO68" s="7"/>
-      <c r="FP68" s="7"/>
-      <c r="FQ68" s="7"/>
-      <c r="FR68" s="7"/>
-      <c r="FS68" s="7"/>
-      <c r="FT68" s="7"/>
-      <c r="FU68" s="7"/>
-      <c r="FV68" s="7"/>
-      <c r="FW68" s="7"/>
-      <c r="FX68" s="7"/>
-      <c r="FY68" s="7"/>
-      <c r="FZ68" s="7"/>
-      <c r="GA68" s="7"/>
-      <c r="GB68" s="7"/>
-      <c r="GC68" s="7"/>
-      <c r="GD68" s="7"/>
-      <c r="GE68" s="7"/>
-      <c r="GF68" s="7"/>
-      <c r="GG68" s="7"/>
-      <c r="GH68" s="7"/>
-      <c r="GI68" s="7"/>
-      <c r="GJ68" s="7"/>
-      <c r="GK68" s="7"/>
-      <c r="GL68" s="7"/>
-      <c r="GM68" s="7"/>
-      <c r="GN68" s="7"/>
-      <c r="GO68" s="7"/>
-      <c r="GP68" s="7"/>
-      <c r="GQ68" s="7"/>
-      <c r="GR68" s="7"/>
-      <c r="GS68" s="7"/>
-      <c r="GT68" s="7"/>
-      <c r="GU68" s="7"/>
-      <c r="GV68" s="7"/>
-      <c r="GW68" s="7"/>
-      <c r="GX68" s="7"/>
-      <c r="GY68" s="7"/>
-      <c r="GZ68" s="7"/>
-      <c r="HA68" s="7"/>
-      <c r="HB68" s="7"/>
-      <c r="HC68" s="7"/>
-      <c r="HD68" s="7"/>
-      <c r="HE68" s="7"/>
-      <c r="HF68" s="7"/>
-      <c r="HG68" s="7"/>
-      <c r="HH68" s="7"/>
-      <c r="HI68" s="7"/>
-      <c r="HJ68" s="7"/>
-      <c r="HK68" s="7"/>
-      <c r="HL68" s="7"/>
-      <c r="HM68" s="7"/>
-      <c r="HN68" s="7"/>
-      <c r="HO68" s="7"/>
-      <c r="HP68" s="7"/>
-      <c r="HQ68" s="7"/>
-      <c r="HR68" s="7"/>
-      <c r="HS68" s="7"/>
-      <c r="HT68" s="7"/>
-      <c r="HU68" s="7"/>
-      <c r="HV68" s="7"/>
-      <c r="HW68" s="7"/>
-      <c r="HX68" s="7"/>
-      <c r="HY68" s="7"/>
-      <c r="HZ68" s="7"/>
-      <c r="IA68" s="7"/>
-      <c r="IB68" s="7"/>
-      <c r="IC68" s="7"/>
-    </row>
-    <row r="69" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="40"/>
       <c r="B69" s="39" t="n">
         <f aca="false">B68+1</f>
@@ -14226,240 +14424,8 @@
         <v>41</v>
       </c>
       <c r="E69" s="40"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
-      <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
-      <c r="M69" s="7"/>
-      <c r="N69" s="7"/>
-      <c r="O69" s="7"/>
-      <c r="P69" s="7"/>
-      <c r="Q69" s="7"/>
-      <c r="R69" s="7"/>
-      <c r="S69" s="7"/>
-      <c r="T69" s="7"/>
-      <c r="U69" s="7"/>
-      <c r="V69" s="7"/>
-      <c r="W69" s="7"/>
-      <c r="X69" s="7"/>
-      <c r="Y69" s="7"/>
-      <c r="Z69" s="7"/>
-      <c r="AA69" s="7"/>
-      <c r="AB69" s="7"/>
-      <c r="AC69" s="7"/>
-      <c r="AD69" s="7"/>
-      <c r="AE69" s="7"/>
-      <c r="AF69" s="7"/>
-      <c r="AG69" s="7"/>
-      <c r="AH69" s="7"/>
-      <c r="AI69" s="7"/>
-      <c r="AJ69" s="7"/>
-      <c r="AK69" s="7"/>
-      <c r="AL69" s="7"/>
-      <c r="AM69" s="7"/>
-      <c r="AN69" s="7"/>
-      <c r="AO69" s="7"/>
-      <c r="AP69" s="7"/>
-      <c r="AQ69" s="7"/>
-      <c r="AR69" s="7"/>
-      <c r="AS69" s="7"/>
-      <c r="AT69" s="7"/>
-      <c r="AU69" s="7"/>
-      <c r="AV69" s="7"/>
-      <c r="AW69" s="7"/>
-      <c r="AX69" s="7"/>
-      <c r="AY69" s="7"/>
-      <c r="AZ69" s="7"/>
-      <c r="BA69" s="7"/>
-      <c r="BB69" s="7"/>
-      <c r="BC69" s="7"/>
-      <c r="BD69" s="7"/>
-      <c r="BE69" s="7"/>
-      <c r="BF69" s="7"/>
-      <c r="BG69" s="7"/>
-      <c r="BH69" s="7"/>
-      <c r="BI69" s="7"/>
-      <c r="BJ69" s="7"/>
-      <c r="BK69" s="7"/>
-      <c r="BL69" s="7"/>
-      <c r="BM69" s="7"/>
-      <c r="BN69" s="7"/>
-      <c r="BO69" s="7"/>
-      <c r="BP69" s="7"/>
-      <c r="BQ69" s="7"/>
-      <c r="BR69" s="7"/>
-      <c r="BS69" s="7"/>
-      <c r="BT69" s="7"/>
-      <c r="BU69" s="7"/>
-      <c r="BV69" s="7"/>
-      <c r="BW69" s="7"/>
-      <c r="BX69" s="7"/>
-      <c r="BY69" s="7"/>
-      <c r="BZ69" s="7"/>
-      <c r="CA69" s="7"/>
-      <c r="CB69" s="7"/>
-      <c r="CC69" s="7"/>
-      <c r="CD69" s="7"/>
-      <c r="CE69" s="7"/>
-      <c r="CF69" s="7"/>
-      <c r="CG69" s="7"/>
-      <c r="CH69" s="7"/>
-      <c r="CI69" s="7"/>
-      <c r="CJ69" s="7"/>
-      <c r="CK69" s="7"/>
-      <c r="CL69" s="7"/>
-      <c r="CM69" s="7"/>
-      <c r="CN69" s="7"/>
-      <c r="CO69" s="7"/>
-      <c r="CP69" s="7"/>
-      <c r="CQ69" s="7"/>
-      <c r="CR69" s="7"/>
-      <c r="CS69" s="7"/>
-      <c r="CT69" s="7"/>
-      <c r="CU69" s="7"/>
-      <c r="CV69" s="7"/>
-      <c r="CW69" s="7"/>
-      <c r="CX69" s="7"/>
-      <c r="CY69" s="7"/>
-      <c r="CZ69" s="7"/>
-      <c r="DA69" s="7"/>
-      <c r="DB69" s="7"/>
-      <c r="DC69" s="7"/>
-      <c r="DD69" s="7"/>
-      <c r="DE69" s="7"/>
-      <c r="DF69" s="7"/>
-      <c r="DG69" s="7"/>
-      <c r="DH69" s="7"/>
-      <c r="DI69" s="7"/>
-      <c r="DJ69" s="7"/>
-      <c r="DK69" s="7"/>
-      <c r="DL69" s="7"/>
-      <c r="DM69" s="7"/>
-      <c r="DN69" s="7"/>
-      <c r="DO69" s="7"/>
-      <c r="DP69" s="7"/>
-      <c r="DQ69" s="7"/>
-      <c r="DR69" s="7"/>
-      <c r="DS69" s="7"/>
-      <c r="DT69" s="7"/>
-      <c r="DU69" s="7"/>
-      <c r="DV69" s="7"/>
-      <c r="DW69" s="7"/>
-      <c r="DX69" s="7"/>
-      <c r="DY69" s="7"/>
-      <c r="DZ69" s="7"/>
-      <c r="EA69" s="7"/>
-      <c r="EB69" s="7"/>
-      <c r="EC69" s="7"/>
-      <c r="ED69" s="7"/>
-      <c r="EE69" s="7"/>
-      <c r="EF69" s="7"/>
-      <c r="EG69" s="7"/>
-      <c r="EH69" s="7"/>
-      <c r="EI69" s="7"/>
-      <c r="EJ69" s="7"/>
-      <c r="EK69" s="7"/>
-      <c r="EL69" s="7"/>
-      <c r="EM69" s="7"/>
-      <c r="EN69" s="7"/>
-      <c r="EO69" s="7"/>
-      <c r="EP69" s="7"/>
-      <c r="EQ69" s="7"/>
-      <c r="ER69" s="7"/>
-      <c r="ES69" s="7"/>
-      <c r="ET69" s="7"/>
-      <c r="EU69" s="7"/>
-      <c r="EV69" s="7"/>
-      <c r="EW69" s="7"/>
-      <c r="EX69" s="7"/>
-      <c r="EY69" s="7"/>
-      <c r="EZ69" s="7"/>
-      <c r="FA69" s="7"/>
-      <c r="FB69" s="7"/>
-      <c r="FC69" s="7"/>
-      <c r="FD69" s="7"/>
-      <c r="FE69" s="7"/>
-      <c r="FF69" s="7"/>
-      <c r="FG69" s="7"/>
-      <c r="FH69" s="7"/>
-      <c r="FI69" s="7"/>
-      <c r="FJ69" s="7"/>
-      <c r="FK69" s="7"/>
-      <c r="FL69" s="7"/>
-      <c r="FM69" s="7"/>
-      <c r="FN69" s="7"/>
-      <c r="FO69" s="7"/>
-      <c r="FP69" s="7"/>
-      <c r="FQ69" s="7"/>
-      <c r="FR69" s="7"/>
-      <c r="FS69" s="7"/>
-      <c r="FT69" s="7"/>
-      <c r="FU69" s="7"/>
-      <c r="FV69" s="7"/>
-      <c r="FW69" s="7"/>
-      <c r="FX69" s="7"/>
-      <c r="FY69" s="7"/>
-      <c r="FZ69" s="7"/>
-      <c r="GA69" s="7"/>
-      <c r="GB69" s="7"/>
-      <c r="GC69" s="7"/>
-      <c r="GD69" s="7"/>
-      <c r="GE69" s="7"/>
-      <c r="GF69" s="7"/>
-      <c r="GG69" s="7"/>
-      <c r="GH69" s="7"/>
-      <c r="GI69" s="7"/>
-      <c r="GJ69" s="7"/>
-      <c r="GK69" s="7"/>
-      <c r="GL69" s="7"/>
-      <c r="GM69" s="7"/>
-      <c r="GN69" s="7"/>
-      <c r="GO69" s="7"/>
-      <c r="GP69" s="7"/>
-      <c r="GQ69" s="7"/>
-      <c r="GR69" s="7"/>
-      <c r="GS69" s="7"/>
-      <c r="GT69" s="7"/>
-      <c r="GU69" s="7"/>
-      <c r="GV69" s="7"/>
-      <c r="GW69" s="7"/>
-      <c r="GX69" s="7"/>
-      <c r="GY69" s="7"/>
-      <c r="GZ69" s="7"/>
-      <c r="HA69" s="7"/>
-      <c r="HB69" s="7"/>
-      <c r="HC69" s="7"/>
-      <c r="HD69" s="7"/>
-      <c r="HE69" s="7"/>
-      <c r="HF69" s="7"/>
-      <c r="HG69" s="7"/>
-      <c r="HH69" s="7"/>
-      <c r="HI69" s="7"/>
-      <c r="HJ69" s="7"/>
-      <c r="HK69" s="7"/>
-      <c r="HL69" s="7"/>
-      <c r="HM69" s="7"/>
-      <c r="HN69" s="7"/>
-      <c r="HO69" s="7"/>
-      <c r="HP69" s="7"/>
-      <c r="HQ69" s="7"/>
-      <c r="HR69" s="7"/>
-      <c r="HS69" s="7"/>
-      <c r="HT69" s="7"/>
-      <c r="HU69" s="7"/>
-      <c r="HV69" s="7"/>
-      <c r="HW69" s="7"/>
-      <c r="HX69" s="7"/>
-      <c r="HY69" s="7"/>
-      <c r="HZ69" s="7"/>
-      <c r="IA69" s="7"/>
-      <c r="IB69" s="7"/>
-      <c r="IC69" s="7"/>
-    </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="70" s="34" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="36"/>
       <c r="B70" s="35" t="n">
         <f aca="false">B69+1</f>
@@ -14472,6 +14438,238 @@
         <v>42</v>
       </c>
       <c r="E70" s="36"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="7"/>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
+      <c r="M70" s="7"/>
+      <c r="N70" s="7"/>
+      <c r="O70" s="7"/>
+      <c r="P70" s="7"/>
+      <c r="Q70" s="7"/>
+      <c r="R70" s="7"/>
+      <c r="S70" s="7"/>
+      <c r="T70" s="7"/>
+      <c r="U70" s="7"/>
+      <c r="V70" s="7"/>
+      <c r="W70" s="7"/>
+      <c r="X70" s="7"/>
+      <c r="Y70" s="7"/>
+      <c r="Z70" s="7"/>
+      <c r="AA70" s="7"/>
+      <c r="AB70" s="7"/>
+      <c r="AC70" s="7"/>
+      <c r="AD70" s="7"/>
+      <c r="AE70" s="7"/>
+      <c r="AF70" s="7"/>
+      <c r="AG70" s="7"/>
+      <c r="AH70" s="7"/>
+      <c r="AI70" s="7"/>
+      <c r="AJ70" s="7"/>
+      <c r="AK70" s="7"/>
+      <c r="AL70" s="7"/>
+      <c r="AM70" s="7"/>
+      <c r="AN70" s="7"/>
+      <c r="AO70" s="7"/>
+      <c r="AP70" s="7"/>
+      <c r="AQ70" s="7"/>
+      <c r="AR70" s="7"/>
+      <c r="AS70" s="7"/>
+      <c r="AT70" s="7"/>
+      <c r="AU70" s="7"/>
+      <c r="AV70" s="7"/>
+      <c r="AW70" s="7"/>
+      <c r="AX70" s="7"/>
+      <c r="AY70" s="7"/>
+      <c r="AZ70" s="7"/>
+      <c r="BA70" s="7"/>
+      <c r="BB70" s="7"/>
+      <c r="BC70" s="7"/>
+      <c r="BD70" s="7"/>
+      <c r="BE70" s="7"/>
+      <c r="BF70" s="7"/>
+      <c r="BG70" s="7"/>
+      <c r="BH70" s="7"/>
+      <c r="BI70" s="7"/>
+      <c r="BJ70" s="7"/>
+      <c r="BK70" s="7"/>
+      <c r="BL70" s="7"/>
+      <c r="BM70" s="7"/>
+      <c r="BN70" s="7"/>
+      <c r="BO70" s="7"/>
+      <c r="BP70" s="7"/>
+      <c r="BQ70" s="7"/>
+      <c r="BR70" s="7"/>
+      <c r="BS70" s="7"/>
+      <c r="BT70" s="7"/>
+      <c r="BU70" s="7"/>
+      <c r="BV70" s="7"/>
+      <c r="BW70" s="7"/>
+      <c r="BX70" s="7"/>
+      <c r="BY70" s="7"/>
+      <c r="BZ70" s="7"/>
+      <c r="CA70" s="7"/>
+      <c r="CB70" s="7"/>
+      <c r="CC70" s="7"/>
+      <c r="CD70" s="7"/>
+      <c r="CE70" s="7"/>
+      <c r="CF70" s="7"/>
+      <c r="CG70" s="7"/>
+      <c r="CH70" s="7"/>
+      <c r="CI70" s="7"/>
+      <c r="CJ70" s="7"/>
+      <c r="CK70" s="7"/>
+      <c r="CL70" s="7"/>
+      <c r="CM70" s="7"/>
+      <c r="CN70" s="7"/>
+      <c r="CO70" s="7"/>
+      <c r="CP70" s="7"/>
+      <c r="CQ70" s="7"/>
+      <c r="CR70" s="7"/>
+      <c r="CS70" s="7"/>
+      <c r="CT70" s="7"/>
+      <c r="CU70" s="7"/>
+      <c r="CV70" s="7"/>
+      <c r="CW70" s="7"/>
+      <c r="CX70" s="7"/>
+      <c r="CY70" s="7"/>
+      <c r="CZ70" s="7"/>
+      <c r="DA70" s="7"/>
+      <c r="DB70" s="7"/>
+      <c r="DC70" s="7"/>
+      <c r="DD70" s="7"/>
+      <c r="DE70" s="7"/>
+      <c r="DF70" s="7"/>
+      <c r="DG70" s="7"/>
+      <c r="DH70" s="7"/>
+      <c r="DI70" s="7"/>
+      <c r="DJ70" s="7"/>
+      <c r="DK70" s="7"/>
+      <c r="DL70" s="7"/>
+      <c r="DM70" s="7"/>
+      <c r="DN70" s="7"/>
+      <c r="DO70" s="7"/>
+      <c r="DP70" s="7"/>
+      <c r="DQ70" s="7"/>
+      <c r="DR70" s="7"/>
+      <c r="DS70" s="7"/>
+      <c r="DT70" s="7"/>
+      <c r="DU70" s="7"/>
+      <c r="DV70" s="7"/>
+      <c r="DW70" s="7"/>
+      <c r="DX70" s="7"/>
+      <c r="DY70" s="7"/>
+      <c r="DZ70" s="7"/>
+      <c r="EA70" s="7"/>
+      <c r="EB70" s="7"/>
+      <c r="EC70" s="7"/>
+      <c r="ED70" s="7"/>
+      <c r="EE70" s="7"/>
+      <c r="EF70" s="7"/>
+      <c r="EG70" s="7"/>
+      <c r="EH70" s="7"/>
+      <c r="EI70" s="7"/>
+      <c r="EJ70" s="7"/>
+      <c r="EK70" s="7"/>
+      <c r="EL70" s="7"/>
+      <c r="EM70" s="7"/>
+      <c r="EN70" s="7"/>
+      <c r="EO70" s="7"/>
+      <c r="EP70" s="7"/>
+      <c r="EQ70" s="7"/>
+      <c r="ER70" s="7"/>
+      <c r="ES70" s="7"/>
+      <c r="ET70" s="7"/>
+      <c r="EU70" s="7"/>
+      <c r="EV70" s="7"/>
+      <c r="EW70" s="7"/>
+      <c r="EX70" s="7"/>
+      <c r="EY70" s="7"/>
+      <c r="EZ70" s="7"/>
+      <c r="FA70" s="7"/>
+      <c r="FB70" s="7"/>
+      <c r="FC70" s="7"/>
+      <c r="FD70" s="7"/>
+      <c r="FE70" s="7"/>
+      <c r="FF70" s="7"/>
+      <c r="FG70" s="7"/>
+      <c r="FH70" s="7"/>
+      <c r="FI70" s="7"/>
+      <c r="FJ70" s="7"/>
+      <c r="FK70" s="7"/>
+      <c r="FL70" s="7"/>
+      <c r="FM70" s="7"/>
+      <c r="FN70" s="7"/>
+      <c r="FO70" s="7"/>
+      <c r="FP70" s="7"/>
+      <c r="FQ70" s="7"/>
+      <c r="FR70" s="7"/>
+      <c r="FS70" s="7"/>
+      <c r="FT70" s="7"/>
+      <c r="FU70" s="7"/>
+      <c r="FV70" s="7"/>
+      <c r="FW70" s="7"/>
+      <c r="FX70" s="7"/>
+      <c r="FY70" s="7"/>
+      <c r="FZ70" s="7"/>
+      <c r="GA70" s="7"/>
+      <c r="GB70" s="7"/>
+      <c r="GC70" s="7"/>
+      <c r="GD70" s="7"/>
+      <c r="GE70" s="7"/>
+      <c r="GF70" s="7"/>
+      <c r="GG70" s="7"/>
+      <c r="GH70" s="7"/>
+      <c r="GI70" s="7"/>
+      <c r="GJ70" s="7"/>
+      <c r="GK70" s="7"/>
+      <c r="GL70" s="7"/>
+      <c r="GM70" s="7"/>
+      <c r="GN70" s="7"/>
+      <c r="GO70" s="7"/>
+      <c r="GP70" s="7"/>
+      <c r="GQ70" s="7"/>
+      <c r="GR70" s="7"/>
+      <c r="GS70" s="7"/>
+      <c r="GT70" s="7"/>
+      <c r="GU70" s="7"/>
+      <c r="GV70" s="7"/>
+      <c r="GW70" s="7"/>
+      <c r="GX70" s="7"/>
+      <c r="GY70" s="7"/>
+      <c r="GZ70" s="7"/>
+      <c r="HA70" s="7"/>
+      <c r="HB70" s="7"/>
+      <c r="HC70" s="7"/>
+      <c r="HD70" s="7"/>
+      <c r="HE70" s="7"/>
+      <c r="HF70" s="7"/>
+      <c r="HG70" s="7"/>
+      <c r="HH70" s="7"/>
+      <c r="HI70" s="7"/>
+      <c r="HJ70" s="7"/>
+      <c r="HK70" s="7"/>
+      <c r="HL70" s="7"/>
+      <c r="HM70" s="7"/>
+      <c r="HN70" s="7"/>
+      <c r="HO70" s="7"/>
+      <c r="HP70" s="7"/>
+      <c r="HQ70" s="7"/>
+      <c r="HR70" s="7"/>
+      <c r="HS70" s="7"/>
+      <c r="HT70" s="7"/>
+      <c r="HU70" s="7"/>
+      <c r="HV70" s="7"/>
+      <c r="HW70" s="7"/>
+      <c r="HX70" s="7"/>
+      <c r="HY70" s="7"/>
+      <c r="HZ70" s="7"/>
+      <c r="IA70" s="7"/>
+      <c r="IB70" s="7"/>
+      <c r="IC70" s="7"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="36"/>
@@ -14487,7 +14685,7 @@
       </c>
       <c r="E71" s="36"/>
     </row>
-    <row r="72" s="34" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="32"/>
       <c r="B72" s="31" t="n">
         <f aca="false">B71+1</f>
@@ -14733,7 +14931,7 @@
       <c r="IB72" s="7"/>
       <c r="IC72" s="7"/>
     </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="32"/>
       <c r="B73" s="31" t="n">
         <f aca="false">B72+1</f>
@@ -14746,6 +14944,238 @@
         <v>45</v>
       </c>
       <c r="E73" s="32"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="7"/>
+      <c r="J73" s="7"/>
+      <c r="K73" s="7"/>
+      <c r="L73" s="7"/>
+      <c r="M73" s="7"/>
+      <c r="N73" s="7"/>
+      <c r="O73" s="7"/>
+      <c r="P73" s="7"/>
+      <c r="Q73" s="7"/>
+      <c r="R73" s="7"/>
+      <c r="S73" s="7"/>
+      <c r="T73" s="7"/>
+      <c r="U73" s="7"/>
+      <c r="V73" s="7"/>
+      <c r="W73" s="7"/>
+      <c r="X73" s="7"/>
+      <c r="Y73" s="7"/>
+      <c r="Z73" s="7"/>
+      <c r="AA73" s="7"/>
+      <c r="AB73" s="7"/>
+      <c r="AC73" s="7"/>
+      <c r="AD73" s="7"/>
+      <c r="AE73" s="7"/>
+      <c r="AF73" s="7"/>
+      <c r="AG73" s="7"/>
+      <c r="AH73" s="7"/>
+      <c r="AI73" s="7"/>
+      <c r="AJ73" s="7"/>
+      <c r="AK73" s="7"/>
+      <c r="AL73" s="7"/>
+      <c r="AM73" s="7"/>
+      <c r="AN73" s="7"/>
+      <c r="AO73" s="7"/>
+      <c r="AP73" s="7"/>
+      <c r="AQ73" s="7"/>
+      <c r="AR73" s="7"/>
+      <c r="AS73" s="7"/>
+      <c r="AT73" s="7"/>
+      <c r="AU73" s="7"/>
+      <c r="AV73" s="7"/>
+      <c r="AW73" s="7"/>
+      <c r="AX73" s="7"/>
+      <c r="AY73" s="7"/>
+      <c r="AZ73" s="7"/>
+      <c r="BA73" s="7"/>
+      <c r="BB73" s="7"/>
+      <c r="BC73" s="7"/>
+      <c r="BD73" s="7"/>
+      <c r="BE73" s="7"/>
+      <c r="BF73" s="7"/>
+      <c r="BG73" s="7"/>
+      <c r="BH73" s="7"/>
+      <c r="BI73" s="7"/>
+      <c r="BJ73" s="7"/>
+      <c r="BK73" s="7"/>
+      <c r="BL73" s="7"/>
+      <c r="BM73" s="7"/>
+      <c r="BN73" s="7"/>
+      <c r="BO73" s="7"/>
+      <c r="BP73" s="7"/>
+      <c r="BQ73" s="7"/>
+      <c r="BR73" s="7"/>
+      <c r="BS73" s="7"/>
+      <c r="BT73" s="7"/>
+      <c r="BU73" s="7"/>
+      <c r="BV73" s="7"/>
+      <c r="BW73" s="7"/>
+      <c r="BX73" s="7"/>
+      <c r="BY73" s="7"/>
+      <c r="BZ73" s="7"/>
+      <c r="CA73" s="7"/>
+      <c r="CB73" s="7"/>
+      <c r="CC73" s="7"/>
+      <c r="CD73" s="7"/>
+      <c r="CE73" s="7"/>
+      <c r="CF73" s="7"/>
+      <c r="CG73" s="7"/>
+      <c r="CH73" s="7"/>
+      <c r="CI73" s="7"/>
+      <c r="CJ73" s="7"/>
+      <c r="CK73" s="7"/>
+      <c r="CL73" s="7"/>
+      <c r="CM73" s="7"/>
+      <c r="CN73" s="7"/>
+      <c r="CO73" s="7"/>
+      <c r="CP73" s="7"/>
+      <c r="CQ73" s="7"/>
+      <c r="CR73" s="7"/>
+      <c r="CS73" s="7"/>
+      <c r="CT73" s="7"/>
+      <c r="CU73" s="7"/>
+      <c r="CV73" s="7"/>
+      <c r="CW73" s="7"/>
+      <c r="CX73" s="7"/>
+      <c r="CY73" s="7"/>
+      <c r="CZ73" s="7"/>
+      <c r="DA73" s="7"/>
+      <c r="DB73" s="7"/>
+      <c r="DC73" s="7"/>
+      <c r="DD73" s="7"/>
+      <c r="DE73" s="7"/>
+      <c r="DF73" s="7"/>
+      <c r="DG73" s="7"/>
+      <c r="DH73" s="7"/>
+      <c r="DI73" s="7"/>
+      <c r="DJ73" s="7"/>
+      <c r="DK73" s="7"/>
+      <c r="DL73" s="7"/>
+      <c r="DM73" s="7"/>
+      <c r="DN73" s="7"/>
+      <c r="DO73" s="7"/>
+      <c r="DP73" s="7"/>
+      <c r="DQ73" s="7"/>
+      <c r="DR73" s="7"/>
+      <c r="DS73" s="7"/>
+      <c r="DT73" s="7"/>
+      <c r="DU73" s="7"/>
+      <c r="DV73" s="7"/>
+      <c r="DW73" s="7"/>
+      <c r="DX73" s="7"/>
+      <c r="DY73" s="7"/>
+      <c r="DZ73" s="7"/>
+      <c r="EA73" s="7"/>
+      <c r="EB73" s="7"/>
+      <c r="EC73" s="7"/>
+      <c r="ED73" s="7"/>
+      <c r="EE73" s="7"/>
+      <c r="EF73" s="7"/>
+      <c r="EG73" s="7"/>
+      <c r="EH73" s="7"/>
+      <c r="EI73" s="7"/>
+      <c r="EJ73" s="7"/>
+      <c r="EK73" s="7"/>
+      <c r="EL73" s="7"/>
+      <c r="EM73" s="7"/>
+      <c r="EN73" s="7"/>
+      <c r="EO73" s="7"/>
+      <c r="EP73" s="7"/>
+      <c r="EQ73" s="7"/>
+      <c r="ER73" s="7"/>
+      <c r="ES73" s="7"/>
+      <c r="ET73" s="7"/>
+      <c r="EU73" s="7"/>
+      <c r="EV73" s="7"/>
+      <c r="EW73" s="7"/>
+      <c r="EX73" s="7"/>
+      <c r="EY73" s="7"/>
+      <c r="EZ73" s="7"/>
+      <c r="FA73" s="7"/>
+      <c r="FB73" s="7"/>
+      <c r="FC73" s="7"/>
+      <c r="FD73" s="7"/>
+      <c r="FE73" s="7"/>
+      <c r="FF73" s="7"/>
+      <c r="FG73" s="7"/>
+      <c r="FH73" s="7"/>
+      <c r="FI73" s="7"/>
+      <c r="FJ73" s="7"/>
+      <c r="FK73" s="7"/>
+      <c r="FL73" s="7"/>
+      <c r="FM73" s="7"/>
+      <c r="FN73" s="7"/>
+      <c r="FO73" s="7"/>
+      <c r="FP73" s="7"/>
+      <c r="FQ73" s="7"/>
+      <c r="FR73" s="7"/>
+      <c r="FS73" s="7"/>
+      <c r="FT73" s="7"/>
+      <c r="FU73" s="7"/>
+      <c r="FV73" s="7"/>
+      <c r="FW73" s="7"/>
+      <c r="FX73" s="7"/>
+      <c r="FY73" s="7"/>
+      <c r="FZ73" s="7"/>
+      <c r="GA73" s="7"/>
+      <c r="GB73" s="7"/>
+      <c r="GC73" s="7"/>
+      <c r="GD73" s="7"/>
+      <c r="GE73" s="7"/>
+      <c r="GF73" s="7"/>
+      <c r="GG73" s="7"/>
+      <c r="GH73" s="7"/>
+      <c r="GI73" s="7"/>
+      <c r="GJ73" s="7"/>
+      <c r="GK73" s="7"/>
+      <c r="GL73" s="7"/>
+      <c r="GM73" s="7"/>
+      <c r="GN73" s="7"/>
+      <c r="GO73" s="7"/>
+      <c r="GP73" s="7"/>
+      <c r="GQ73" s="7"/>
+      <c r="GR73" s="7"/>
+      <c r="GS73" s="7"/>
+      <c r="GT73" s="7"/>
+      <c r="GU73" s="7"/>
+      <c r="GV73" s="7"/>
+      <c r="GW73" s="7"/>
+      <c r="GX73" s="7"/>
+      <c r="GY73" s="7"/>
+      <c r="GZ73" s="7"/>
+      <c r="HA73" s="7"/>
+      <c r="HB73" s="7"/>
+      <c r="HC73" s="7"/>
+      <c r="HD73" s="7"/>
+      <c r="HE73" s="7"/>
+      <c r="HF73" s="7"/>
+      <c r="HG73" s="7"/>
+      <c r="HH73" s="7"/>
+      <c r="HI73" s="7"/>
+      <c r="HJ73" s="7"/>
+      <c r="HK73" s="7"/>
+      <c r="HL73" s="7"/>
+      <c r="HM73" s="7"/>
+      <c r="HN73" s="7"/>
+      <c r="HO73" s="7"/>
+      <c r="HP73" s="7"/>
+      <c r="HQ73" s="7"/>
+      <c r="HR73" s="7"/>
+      <c r="HS73" s="7"/>
+      <c r="HT73" s="7"/>
+      <c r="HU73" s="7"/>
+      <c r="HV73" s="7"/>
+      <c r="HW73" s="7"/>
+      <c r="HX73" s="7"/>
+      <c r="HY73" s="7"/>
+      <c r="HZ73" s="7"/>
+      <c r="IA73" s="7"/>
+      <c r="IB73" s="7"/>
+      <c r="IC73" s="7"/>
     </row>
     <row r="74" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="36"/>
@@ -14995,7 +15425,7 @@
       <c r="IB74" s="7"/>
       <c r="IC74" s="7"/>
     </row>
-    <row r="75" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="36"/>
       <c r="B75" s="35" t="n">
         <f aca="false">B74+1</f>
@@ -15008,240 +15438,8 @@
         <v>47</v>
       </c>
       <c r="E75" s="36"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="7"/>
-      <c r="K75" s="7"/>
-      <c r="L75" s="7"/>
-      <c r="M75" s="7"/>
-      <c r="N75" s="7"/>
-      <c r="O75" s="7"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="7"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="7"/>
-      <c r="T75" s="7"/>
-      <c r="U75" s="7"/>
-      <c r="V75" s="7"/>
-      <c r="W75" s="7"/>
-      <c r="X75" s="7"/>
-      <c r="Y75" s="7"/>
-      <c r="Z75" s="7"/>
-      <c r="AA75" s="7"/>
-      <c r="AB75" s="7"/>
-      <c r="AC75" s="7"/>
-      <c r="AD75" s="7"/>
-      <c r="AE75" s="7"/>
-      <c r="AF75" s="7"/>
-      <c r="AG75" s="7"/>
-      <c r="AH75" s="7"/>
-      <c r="AI75" s="7"/>
-      <c r="AJ75" s="7"/>
-      <c r="AK75" s="7"/>
-      <c r="AL75" s="7"/>
-      <c r="AM75" s="7"/>
-      <c r="AN75" s="7"/>
-      <c r="AO75" s="7"/>
-      <c r="AP75" s="7"/>
-      <c r="AQ75" s="7"/>
-      <c r="AR75" s="7"/>
-      <c r="AS75" s="7"/>
-      <c r="AT75" s="7"/>
-      <c r="AU75" s="7"/>
-      <c r="AV75" s="7"/>
-      <c r="AW75" s="7"/>
-      <c r="AX75" s="7"/>
-      <c r="AY75" s="7"/>
-      <c r="AZ75" s="7"/>
-      <c r="BA75" s="7"/>
-      <c r="BB75" s="7"/>
-      <c r="BC75" s="7"/>
-      <c r="BD75" s="7"/>
-      <c r="BE75" s="7"/>
-      <c r="BF75" s="7"/>
-      <c r="BG75" s="7"/>
-      <c r="BH75" s="7"/>
-      <c r="BI75" s="7"/>
-      <c r="BJ75" s="7"/>
-      <c r="BK75" s="7"/>
-      <c r="BL75" s="7"/>
-      <c r="BM75" s="7"/>
-      <c r="BN75" s="7"/>
-      <c r="BO75" s="7"/>
-      <c r="BP75" s="7"/>
-      <c r="BQ75" s="7"/>
-      <c r="BR75" s="7"/>
-      <c r="BS75" s="7"/>
-      <c r="BT75" s="7"/>
-      <c r="BU75" s="7"/>
-      <c r="BV75" s="7"/>
-      <c r="BW75" s="7"/>
-      <c r="BX75" s="7"/>
-      <c r="BY75" s="7"/>
-      <c r="BZ75" s="7"/>
-      <c r="CA75" s="7"/>
-      <c r="CB75" s="7"/>
-      <c r="CC75" s="7"/>
-      <c r="CD75" s="7"/>
-      <c r="CE75" s="7"/>
-      <c r="CF75" s="7"/>
-      <c r="CG75" s="7"/>
-      <c r="CH75" s="7"/>
-      <c r="CI75" s="7"/>
-      <c r="CJ75" s="7"/>
-      <c r="CK75" s="7"/>
-      <c r="CL75" s="7"/>
-      <c r="CM75" s="7"/>
-      <c r="CN75" s="7"/>
-      <c r="CO75" s="7"/>
-      <c r="CP75" s="7"/>
-      <c r="CQ75" s="7"/>
-      <c r="CR75" s="7"/>
-      <c r="CS75" s="7"/>
-      <c r="CT75" s="7"/>
-      <c r="CU75" s="7"/>
-      <c r="CV75" s="7"/>
-      <c r="CW75" s="7"/>
-      <c r="CX75" s="7"/>
-      <c r="CY75" s="7"/>
-      <c r="CZ75" s="7"/>
-      <c r="DA75" s="7"/>
-      <c r="DB75" s="7"/>
-      <c r="DC75" s="7"/>
-      <c r="DD75" s="7"/>
-      <c r="DE75" s="7"/>
-      <c r="DF75" s="7"/>
-      <c r="DG75" s="7"/>
-      <c r="DH75" s="7"/>
-      <c r="DI75" s="7"/>
-      <c r="DJ75" s="7"/>
-      <c r="DK75" s="7"/>
-      <c r="DL75" s="7"/>
-      <c r="DM75" s="7"/>
-      <c r="DN75" s="7"/>
-      <c r="DO75" s="7"/>
-      <c r="DP75" s="7"/>
-      <c r="DQ75" s="7"/>
-      <c r="DR75" s="7"/>
-      <c r="DS75" s="7"/>
-      <c r="DT75" s="7"/>
-      <c r="DU75" s="7"/>
-      <c r="DV75" s="7"/>
-      <c r="DW75" s="7"/>
-      <c r="DX75" s="7"/>
-      <c r="DY75" s="7"/>
-      <c r="DZ75" s="7"/>
-      <c r="EA75" s="7"/>
-      <c r="EB75" s="7"/>
-      <c r="EC75" s="7"/>
-      <c r="ED75" s="7"/>
-      <c r="EE75" s="7"/>
-      <c r="EF75" s="7"/>
-      <c r="EG75" s="7"/>
-      <c r="EH75" s="7"/>
-      <c r="EI75" s="7"/>
-      <c r="EJ75" s="7"/>
-      <c r="EK75" s="7"/>
-      <c r="EL75" s="7"/>
-      <c r="EM75" s="7"/>
-      <c r="EN75" s="7"/>
-      <c r="EO75" s="7"/>
-      <c r="EP75" s="7"/>
-      <c r="EQ75" s="7"/>
-      <c r="ER75" s="7"/>
-      <c r="ES75" s="7"/>
-      <c r="ET75" s="7"/>
-      <c r="EU75" s="7"/>
-      <c r="EV75" s="7"/>
-      <c r="EW75" s="7"/>
-      <c r="EX75" s="7"/>
-      <c r="EY75" s="7"/>
-      <c r="EZ75" s="7"/>
-      <c r="FA75" s="7"/>
-      <c r="FB75" s="7"/>
-      <c r="FC75" s="7"/>
-      <c r="FD75" s="7"/>
-      <c r="FE75" s="7"/>
-      <c r="FF75" s="7"/>
-      <c r="FG75" s="7"/>
-      <c r="FH75" s="7"/>
-      <c r="FI75" s="7"/>
-      <c r="FJ75" s="7"/>
-      <c r="FK75" s="7"/>
-      <c r="FL75" s="7"/>
-      <c r="FM75" s="7"/>
-      <c r="FN75" s="7"/>
-      <c r="FO75" s="7"/>
-      <c r="FP75" s="7"/>
-      <c r="FQ75" s="7"/>
-      <c r="FR75" s="7"/>
-      <c r="FS75" s="7"/>
-      <c r="FT75" s="7"/>
-      <c r="FU75" s="7"/>
-      <c r="FV75" s="7"/>
-      <c r="FW75" s="7"/>
-      <c r="FX75" s="7"/>
-      <c r="FY75" s="7"/>
-      <c r="FZ75" s="7"/>
-      <c r="GA75" s="7"/>
-      <c r="GB75" s="7"/>
-      <c r="GC75" s="7"/>
-      <c r="GD75" s="7"/>
-      <c r="GE75" s="7"/>
-      <c r="GF75" s="7"/>
-      <c r="GG75" s="7"/>
-      <c r="GH75" s="7"/>
-      <c r="GI75" s="7"/>
-      <c r="GJ75" s="7"/>
-      <c r="GK75" s="7"/>
-      <c r="GL75" s="7"/>
-      <c r="GM75" s="7"/>
-      <c r="GN75" s="7"/>
-      <c r="GO75" s="7"/>
-      <c r="GP75" s="7"/>
-      <c r="GQ75" s="7"/>
-      <c r="GR75" s="7"/>
-      <c r="GS75" s="7"/>
-      <c r="GT75" s="7"/>
-      <c r="GU75" s="7"/>
-      <c r="GV75" s="7"/>
-      <c r="GW75" s="7"/>
-      <c r="GX75" s="7"/>
-      <c r="GY75" s="7"/>
-      <c r="GZ75" s="7"/>
-      <c r="HA75" s="7"/>
-      <c r="HB75" s="7"/>
-      <c r="HC75" s="7"/>
-      <c r="HD75" s="7"/>
-      <c r="HE75" s="7"/>
-      <c r="HF75" s="7"/>
-      <c r="HG75" s="7"/>
-      <c r="HH75" s="7"/>
-      <c r="HI75" s="7"/>
-      <c r="HJ75" s="7"/>
-      <c r="HK75" s="7"/>
-      <c r="HL75" s="7"/>
-      <c r="HM75" s="7"/>
-      <c r="HN75" s="7"/>
-      <c r="HO75" s="7"/>
-      <c r="HP75" s="7"/>
-      <c r="HQ75" s="7"/>
-      <c r="HR75" s="7"/>
-      <c r="HS75" s="7"/>
-      <c r="HT75" s="7"/>
-      <c r="HU75" s="7"/>
-      <c r="HV75" s="7"/>
-      <c r="HW75" s="7"/>
-      <c r="HX75" s="7"/>
-      <c r="HY75" s="7"/>
-      <c r="HZ75" s="7"/>
-      <c r="IA75" s="7"/>
-      <c r="IB75" s="7"/>
-      <c r="IC75" s="7"/>
-    </row>
-    <row r="76" s="25" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="40"/>
       <c r="B76" s="39" t="n">
         <f aca="false">B75+1</f>
@@ -15254,240 +15452,8 @@
         <v>48</v>
       </c>
       <c r="E76" s="40"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="7"/>
-      <c r="O76" s="7"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="7"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="7"/>
-      <c r="T76" s="7"/>
-      <c r="U76" s="7"/>
-      <c r="V76" s="7"/>
-      <c r="W76" s="7"/>
-      <c r="X76" s="7"/>
-      <c r="Y76" s="7"/>
-      <c r="Z76" s="7"/>
-      <c r="AA76" s="7"/>
-      <c r="AB76" s="7"/>
-      <c r="AC76" s="7"/>
-      <c r="AD76" s="7"/>
-      <c r="AE76" s="7"/>
-      <c r="AF76" s="7"/>
-      <c r="AG76" s="7"/>
-      <c r="AH76" s="7"/>
-      <c r="AI76" s="7"/>
-      <c r="AJ76" s="7"/>
-      <c r="AK76" s="7"/>
-      <c r="AL76" s="7"/>
-      <c r="AM76" s="7"/>
-      <c r="AN76" s="7"/>
-      <c r="AO76" s="7"/>
-      <c r="AP76" s="7"/>
-      <c r="AQ76" s="7"/>
-      <c r="AR76" s="7"/>
-      <c r="AS76" s="7"/>
-      <c r="AT76" s="7"/>
-      <c r="AU76" s="7"/>
-      <c r="AV76" s="7"/>
-      <c r="AW76" s="7"/>
-      <c r="AX76" s="7"/>
-      <c r="AY76" s="7"/>
-      <c r="AZ76" s="7"/>
-      <c r="BA76" s="7"/>
-      <c r="BB76" s="7"/>
-      <c r="BC76" s="7"/>
-      <c r="BD76" s="7"/>
-      <c r="BE76" s="7"/>
-      <c r="BF76" s="7"/>
-      <c r="BG76" s="7"/>
-      <c r="BH76" s="7"/>
-      <c r="BI76" s="7"/>
-      <c r="BJ76" s="7"/>
-      <c r="BK76" s="7"/>
-      <c r="BL76" s="7"/>
-      <c r="BM76" s="7"/>
-      <c r="BN76" s="7"/>
-      <c r="BO76" s="7"/>
-      <c r="BP76" s="7"/>
-      <c r="BQ76" s="7"/>
-      <c r="BR76" s="7"/>
-      <c r="BS76" s="7"/>
-      <c r="BT76" s="7"/>
-      <c r="BU76" s="7"/>
-      <c r="BV76" s="7"/>
-      <c r="BW76" s="7"/>
-      <c r="BX76" s="7"/>
-      <c r="BY76" s="7"/>
-      <c r="BZ76" s="7"/>
-      <c r="CA76" s="7"/>
-      <c r="CB76" s="7"/>
-      <c r="CC76" s="7"/>
-      <c r="CD76" s="7"/>
-      <c r="CE76" s="7"/>
-      <c r="CF76" s="7"/>
-      <c r="CG76" s="7"/>
-      <c r="CH76" s="7"/>
-      <c r="CI76" s="7"/>
-      <c r="CJ76" s="7"/>
-      <c r="CK76" s="7"/>
-      <c r="CL76" s="7"/>
-      <c r="CM76" s="7"/>
-      <c r="CN76" s="7"/>
-      <c r="CO76" s="7"/>
-      <c r="CP76" s="7"/>
-      <c r="CQ76" s="7"/>
-      <c r="CR76" s="7"/>
-      <c r="CS76" s="7"/>
-      <c r="CT76" s="7"/>
-      <c r="CU76" s="7"/>
-      <c r="CV76" s="7"/>
-      <c r="CW76" s="7"/>
-      <c r="CX76" s="7"/>
-      <c r="CY76" s="7"/>
-      <c r="CZ76" s="7"/>
-      <c r="DA76" s="7"/>
-      <c r="DB76" s="7"/>
-      <c r="DC76" s="7"/>
-      <c r="DD76" s="7"/>
-      <c r="DE76" s="7"/>
-      <c r="DF76" s="7"/>
-      <c r="DG76" s="7"/>
-      <c r="DH76" s="7"/>
-      <c r="DI76" s="7"/>
-      <c r="DJ76" s="7"/>
-      <c r="DK76" s="7"/>
-      <c r="DL76" s="7"/>
-      <c r="DM76" s="7"/>
-      <c r="DN76" s="7"/>
-      <c r="DO76" s="7"/>
-      <c r="DP76" s="7"/>
-      <c r="DQ76" s="7"/>
-      <c r="DR76" s="7"/>
-      <c r="DS76" s="7"/>
-      <c r="DT76" s="7"/>
-      <c r="DU76" s="7"/>
-      <c r="DV76" s="7"/>
-      <c r="DW76" s="7"/>
-      <c r="DX76" s="7"/>
-      <c r="DY76" s="7"/>
-      <c r="DZ76" s="7"/>
-      <c r="EA76" s="7"/>
-      <c r="EB76" s="7"/>
-      <c r="EC76" s="7"/>
-      <c r="ED76" s="7"/>
-      <c r="EE76" s="7"/>
-      <c r="EF76" s="7"/>
-      <c r="EG76" s="7"/>
-      <c r="EH76" s="7"/>
-      <c r="EI76" s="7"/>
-      <c r="EJ76" s="7"/>
-      <c r="EK76" s="7"/>
-      <c r="EL76" s="7"/>
-      <c r="EM76" s="7"/>
-      <c r="EN76" s="7"/>
-      <c r="EO76" s="7"/>
-      <c r="EP76" s="7"/>
-      <c r="EQ76" s="7"/>
-      <c r="ER76" s="7"/>
-      <c r="ES76" s="7"/>
-      <c r="ET76" s="7"/>
-      <c r="EU76" s="7"/>
-      <c r="EV76" s="7"/>
-      <c r="EW76" s="7"/>
-      <c r="EX76" s="7"/>
-      <c r="EY76" s="7"/>
-      <c r="EZ76" s="7"/>
-      <c r="FA76" s="7"/>
-      <c r="FB76" s="7"/>
-      <c r="FC76" s="7"/>
-      <c r="FD76" s="7"/>
-      <c r="FE76" s="7"/>
-      <c r="FF76" s="7"/>
-      <c r="FG76" s="7"/>
-      <c r="FH76" s="7"/>
-      <c r="FI76" s="7"/>
-      <c r="FJ76" s="7"/>
-      <c r="FK76" s="7"/>
-      <c r="FL76" s="7"/>
-      <c r="FM76" s="7"/>
-      <c r="FN76" s="7"/>
-      <c r="FO76" s="7"/>
-      <c r="FP76" s="7"/>
-      <c r="FQ76" s="7"/>
-      <c r="FR76" s="7"/>
-      <c r="FS76" s="7"/>
-      <c r="FT76" s="7"/>
-      <c r="FU76" s="7"/>
-      <c r="FV76" s="7"/>
-      <c r="FW76" s="7"/>
-      <c r="FX76" s="7"/>
-      <c r="FY76" s="7"/>
-      <c r="FZ76" s="7"/>
-      <c r="GA76" s="7"/>
-      <c r="GB76" s="7"/>
-      <c r="GC76" s="7"/>
-      <c r="GD76" s="7"/>
-      <c r="GE76" s="7"/>
-      <c r="GF76" s="7"/>
-      <c r="GG76" s="7"/>
-      <c r="GH76" s="7"/>
-      <c r="GI76" s="7"/>
-      <c r="GJ76" s="7"/>
-      <c r="GK76" s="7"/>
-      <c r="GL76" s="7"/>
-      <c r="GM76" s="7"/>
-      <c r="GN76" s="7"/>
-      <c r="GO76" s="7"/>
-      <c r="GP76" s="7"/>
-      <c r="GQ76" s="7"/>
-      <c r="GR76" s="7"/>
-      <c r="GS76" s="7"/>
-      <c r="GT76" s="7"/>
-      <c r="GU76" s="7"/>
-      <c r="GV76" s="7"/>
-      <c r="GW76" s="7"/>
-      <c r="GX76" s="7"/>
-      <c r="GY76" s="7"/>
-      <c r="GZ76" s="7"/>
-      <c r="HA76" s="7"/>
-      <c r="HB76" s="7"/>
-      <c r="HC76" s="7"/>
-      <c r="HD76" s="7"/>
-      <c r="HE76" s="7"/>
-      <c r="HF76" s="7"/>
-      <c r="HG76" s="7"/>
-      <c r="HH76" s="7"/>
-      <c r="HI76" s="7"/>
-      <c r="HJ76" s="7"/>
-      <c r="HK76" s="7"/>
-      <c r="HL76" s="7"/>
-      <c r="HM76" s="7"/>
-      <c r="HN76" s="7"/>
-      <c r="HO76" s="7"/>
-      <c r="HP76" s="7"/>
-      <c r="HQ76" s="7"/>
-      <c r="HR76" s="7"/>
-      <c r="HS76" s="7"/>
-      <c r="HT76" s="7"/>
-      <c r="HU76" s="7"/>
-      <c r="HV76" s="7"/>
-      <c r="HW76" s="7"/>
-      <c r="HX76" s="7"/>
-      <c r="HY76" s="7"/>
-      <c r="HZ76" s="7"/>
-      <c r="IA76" s="7"/>
-      <c r="IB76" s="7"/>
-      <c r="IC76" s="7"/>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="77" s="34" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="36"/>
       <c r="B77" s="35" t="n">
         <f aca="false">B76+1</f>
@@ -15500,6 +15466,238 @@
         <v>49</v>
       </c>
       <c r="E77" s="36"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
+      <c r="J77" s="7"/>
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+      <c r="M77" s="7"/>
+      <c r="N77" s="7"/>
+      <c r="O77" s="7"/>
+      <c r="P77" s="7"/>
+      <c r="Q77" s="7"/>
+      <c r="R77" s="7"/>
+      <c r="S77" s="7"/>
+      <c r="T77" s="7"/>
+      <c r="U77" s="7"/>
+      <c r="V77" s="7"/>
+      <c r="W77" s="7"/>
+      <c r="X77" s="7"/>
+      <c r="Y77" s="7"/>
+      <c r="Z77" s="7"/>
+      <c r="AA77" s="7"/>
+      <c r="AB77" s="7"/>
+      <c r="AC77" s="7"/>
+      <c r="AD77" s="7"/>
+      <c r="AE77" s="7"/>
+      <c r="AF77" s="7"/>
+      <c r="AG77" s="7"/>
+      <c r="AH77" s="7"/>
+      <c r="AI77" s="7"/>
+      <c r="AJ77" s="7"/>
+      <c r="AK77" s="7"/>
+      <c r="AL77" s="7"/>
+      <c r="AM77" s="7"/>
+      <c r="AN77" s="7"/>
+      <c r="AO77" s="7"/>
+      <c r="AP77" s="7"/>
+      <c r="AQ77" s="7"/>
+      <c r="AR77" s="7"/>
+      <c r="AS77" s="7"/>
+      <c r="AT77" s="7"/>
+      <c r="AU77" s="7"/>
+      <c r="AV77" s="7"/>
+      <c r="AW77" s="7"/>
+      <c r="AX77" s="7"/>
+      <c r="AY77" s="7"/>
+      <c r="AZ77" s="7"/>
+      <c r="BA77" s="7"/>
+      <c r="BB77" s="7"/>
+      <c r="BC77" s="7"/>
+      <c r="BD77" s="7"/>
+      <c r="BE77" s="7"/>
+      <c r="BF77" s="7"/>
+      <c r="BG77" s="7"/>
+      <c r="BH77" s="7"/>
+      <c r="BI77" s="7"/>
+      <c r="BJ77" s="7"/>
+      <c r="BK77" s="7"/>
+      <c r="BL77" s="7"/>
+      <c r="BM77" s="7"/>
+      <c r="BN77" s="7"/>
+      <c r="BO77" s="7"/>
+      <c r="BP77" s="7"/>
+      <c r="BQ77" s="7"/>
+      <c r="BR77" s="7"/>
+      <c r="BS77" s="7"/>
+      <c r="BT77" s="7"/>
+      <c r="BU77" s="7"/>
+      <c r="BV77" s="7"/>
+      <c r="BW77" s="7"/>
+      <c r="BX77" s="7"/>
+      <c r="BY77" s="7"/>
+      <c r="BZ77" s="7"/>
+      <c r="CA77" s="7"/>
+      <c r="CB77" s="7"/>
+      <c r="CC77" s="7"/>
+      <c r="CD77" s="7"/>
+      <c r="CE77" s="7"/>
+      <c r="CF77" s="7"/>
+      <c r="CG77" s="7"/>
+      <c r="CH77" s="7"/>
+      <c r="CI77" s="7"/>
+      <c r="CJ77" s="7"/>
+      <c r="CK77" s="7"/>
+      <c r="CL77" s="7"/>
+      <c r="CM77" s="7"/>
+      <c r="CN77" s="7"/>
+      <c r="CO77" s="7"/>
+      <c r="CP77" s="7"/>
+      <c r="CQ77" s="7"/>
+      <c r="CR77" s="7"/>
+      <c r="CS77" s="7"/>
+      <c r="CT77" s="7"/>
+      <c r="CU77" s="7"/>
+      <c r="CV77" s="7"/>
+      <c r="CW77" s="7"/>
+      <c r="CX77" s="7"/>
+      <c r="CY77" s="7"/>
+      <c r="CZ77" s="7"/>
+      <c r="DA77" s="7"/>
+      <c r="DB77" s="7"/>
+      <c r="DC77" s="7"/>
+      <c r="DD77" s="7"/>
+      <c r="DE77" s="7"/>
+      <c r="DF77" s="7"/>
+      <c r="DG77" s="7"/>
+      <c r="DH77" s="7"/>
+      <c r="DI77" s="7"/>
+      <c r="DJ77" s="7"/>
+      <c r="DK77" s="7"/>
+      <c r="DL77" s="7"/>
+      <c r="DM77" s="7"/>
+      <c r="DN77" s="7"/>
+      <c r="DO77" s="7"/>
+      <c r="DP77" s="7"/>
+      <c r="DQ77" s="7"/>
+      <c r="DR77" s="7"/>
+      <c r="DS77" s="7"/>
+      <c r="DT77" s="7"/>
+      <c r="DU77" s="7"/>
+      <c r="DV77" s="7"/>
+      <c r="DW77" s="7"/>
+      <c r="DX77" s="7"/>
+      <c r="DY77" s="7"/>
+      <c r="DZ77" s="7"/>
+      <c r="EA77" s="7"/>
+      <c r="EB77" s="7"/>
+      <c r="EC77" s="7"/>
+      <c r="ED77" s="7"/>
+      <c r="EE77" s="7"/>
+      <c r="EF77" s="7"/>
+      <c r="EG77" s="7"/>
+      <c r="EH77" s="7"/>
+      <c r="EI77" s="7"/>
+      <c r="EJ77" s="7"/>
+      <c r="EK77" s="7"/>
+      <c r="EL77" s="7"/>
+      <c r="EM77" s="7"/>
+      <c r="EN77" s="7"/>
+      <c r="EO77" s="7"/>
+      <c r="EP77" s="7"/>
+      <c r="EQ77" s="7"/>
+      <c r="ER77" s="7"/>
+      <c r="ES77" s="7"/>
+      <c r="ET77" s="7"/>
+      <c r="EU77" s="7"/>
+      <c r="EV77" s="7"/>
+      <c r="EW77" s="7"/>
+      <c r="EX77" s="7"/>
+      <c r="EY77" s="7"/>
+      <c r="EZ77" s="7"/>
+      <c r="FA77" s="7"/>
+      <c r="FB77" s="7"/>
+      <c r="FC77" s="7"/>
+      <c r="FD77" s="7"/>
+      <c r="FE77" s="7"/>
+      <c r="FF77" s="7"/>
+      <c r="FG77" s="7"/>
+      <c r="FH77" s="7"/>
+      <c r="FI77" s="7"/>
+      <c r="FJ77" s="7"/>
+      <c r="FK77" s="7"/>
+      <c r="FL77" s="7"/>
+      <c r="FM77" s="7"/>
+      <c r="FN77" s="7"/>
+      <c r="FO77" s="7"/>
+      <c r="FP77" s="7"/>
+      <c r="FQ77" s="7"/>
+      <c r="FR77" s="7"/>
+      <c r="FS77" s="7"/>
+      <c r="FT77" s="7"/>
+      <c r="FU77" s="7"/>
+      <c r="FV77" s="7"/>
+      <c r="FW77" s="7"/>
+      <c r="FX77" s="7"/>
+      <c r="FY77" s="7"/>
+      <c r="FZ77" s="7"/>
+      <c r="GA77" s="7"/>
+      <c r="GB77" s="7"/>
+      <c r="GC77" s="7"/>
+      <c r="GD77" s="7"/>
+      <c r="GE77" s="7"/>
+      <c r="GF77" s="7"/>
+      <c r="GG77" s="7"/>
+      <c r="GH77" s="7"/>
+      <c r="GI77" s="7"/>
+      <c r="GJ77" s="7"/>
+      <c r="GK77" s="7"/>
+      <c r="GL77" s="7"/>
+      <c r="GM77" s="7"/>
+      <c r="GN77" s="7"/>
+      <c r="GO77" s="7"/>
+      <c r="GP77" s="7"/>
+      <c r="GQ77" s="7"/>
+      <c r="GR77" s="7"/>
+      <c r="GS77" s="7"/>
+      <c r="GT77" s="7"/>
+      <c r="GU77" s="7"/>
+      <c r="GV77" s="7"/>
+      <c r="GW77" s="7"/>
+      <c r="GX77" s="7"/>
+      <c r="GY77" s="7"/>
+      <c r="GZ77" s="7"/>
+      <c r="HA77" s="7"/>
+      <c r="HB77" s="7"/>
+      <c r="HC77" s="7"/>
+      <c r="HD77" s="7"/>
+      <c r="HE77" s="7"/>
+      <c r="HF77" s="7"/>
+      <c r="HG77" s="7"/>
+      <c r="HH77" s="7"/>
+      <c r="HI77" s="7"/>
+      <c r="HJ77" s="7"/>
+      <c r="HK77" s="7"/>
+      <c r="HL77" s="7"/>
+      <c r="HM77" s="7"/>
+      <c r="HN77" s="7"/>
+      <c r="HO77" s="7"/>
+      <c r="HP77" s="7"/>
+      <c r="HQ77" s="7"/>
+      <c r="HR77" s="7"/>
+      <c r="HS77" s="7"/>
+      <c r="HT77" s="7"/>
+      <c r="HU77" s="7"/>
+      <c r="HV77" s="7"/>
+      <c r="HW77" s="7"/>
+      <c r="HX77" s="7"/>
+      <c r="HY77" s="7"/>
+      <c r="HZ77" s="7"/>
+      <c r="IA77" s="7"/>
+      <c r="IB77" s="7"/>
+      <c r="IC77" s="7"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="36"/>
@@ -15515,7 +15713,7 @@
       </c>
       <c r="E78" s="36"/>
     </row>
-    <row r="79" s="34" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="32"/>
       <c r="B79" s="31" t="n">
         <f aca="false">B78+1</f>
@@ -15528,238 +15726,6 @@
         <v>51</v>
       </c>
       <c r="E79" s="32"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7"/>
-      <c r="J79" s="7"/>
-      <c r="K79" s="7"/>
-      <c r="L79" s="7"/>
-      <c r="M79" s="7"/>
-      <c r="N79" s="7"/>
-      <c r="O79" s="7"/>
-      <c r="P79" s="7"/>
-      <c r="Q79" s="7"/>
-      <c r="R79" s="7"/>
-      <c r="S79" s="7"/>
-      <c r="T79" s="7"/>
-      <c r="U79" s="7"/>
-      <c r="V79" s="7"/>
-      <c r="W79" s="7"/>
-      <c r="X79" s="7"/>
-      <c r="Y79" s="7"/>
-      <c r="Z79" s="7"/>
-      <c r="AA79" s="7"/>
-      <c r="AB79" s="7"/>
-      <c r="AC79" s="7"/>
-      <c r="AD79" s="7"/>
-      <c r="AE79" s="7"/>
-      <c r="AF79" s="7"/>
-      <c r="AG79" s="7"/>
-      <c r="AH79" s="7"/>
-      <c r="AI79" s="7"/>
-      <c r="AJ79" s="7"/>
-      <c r="AK79" s="7"/>
-      <c r="AL79" s="7"/>
-      <c r="AM79" s="7"/>
-      <c r="AN79" s="7"/>
-      <c r="AO79" s="7"/>
-      <c r="AP79" s="7"/>
-      <c r="AQ79" s="7"/>
-      <c r="AR79" s="7"/>
-      <c r="AS79" s="7"/>
-      <c r="AT79" s="7"/>
-      <c r="AU79" s="7"/>
-      <c r="AV79" s="7"/>
-      <c r="AW79" s="7"/>
-      <c r="AX79" s="7"/>
-      <c r="AY79" s="7"/>
-      <c r="AZ79" s="7"/>
-      <c r="BA79" s="7"/>
-      <c r="BB79" s="7"/>
-      <c r="BC79" s="7"/>
-      <c r="BD79" s="7"/>
-      <c r="BE79" s="7"/>
-      <c r="BF79" s="7"/>
-      <c r="BG79" s="7"/>
-      <c r="BH79" s="7"/>
-      <c r="BI79" s="7"/>
-      <c r="BJ79" s="7"/>
-      <c r="BK79" s="7"/>
-      <c r="BL79" s="7"/>
-      <c r="BM79" s="7"/>
-      <c r="BN79" s="7"/>
-      <c r="BO79" s="7"/>
-      <c r="BP79" s="7"/>
-      <c r="BQ79" s="7"/>
-      <c r="BR79" s="7"/>
-      <c r="BS79" s="7"/>
-      <c r="BT79" s="7"/>
-      <c r="BU79" s="7"/>
-      <c r="BV79" s="7"/>
-      <c r="BW79" s="7"/>
-      <c r="BX79" s="7"/>
-      <c r="BY79" s="7"/>
-      <c r="BZ79" s="7"/>
-      <c r="CA79" s="7"/>
-      <c r="CB79" s="7"/>
-      <c r="CC79" s="7"/>
-      <c r="CD79" s="7"/>
-      <c r="CE79" s="7"/>
-      <c r="CF79" s="7"/>
-      <c r="CG79" s="7"/>
-      <c r="CH79" s="7"/>
-      <c r="CI79" s="7"/>
-      <c r="CJ79" s="7"/>
-      <c r="CK79" s="7"/>
-      <c r="CL79" s="7"/>
-      <c r="CM79" s="7"/>
-      <c r="CN79" s="7"/>
-      <c r="CO79" s="7"/>
-      <c r="CP79" s="7"/>
-      <c r="CQ79" s="7"/>
-      <c r="CR79" s="7"/>
-      <c r="CS79" s="7"/>
-      <c r="CT79" s="7"/>
-      <c r="CU79" s="7"/>
-      <c r="CV79" s="7"/>
-      <c r="CW79" s="7"/>
-      <c r="CX79" s="7"/>
-      <c r="CY79" s="7"/>
-      <c r="CZ79" s="7"/>
-      <c r="DA79" s="7"/>
-      <c r="DB79" s="7"/>
-      <c r="DC79" s="7"/>
-      <c r="DD79" s="7"/>
-      <c r="DE79" s="7"/>
-      <c r="DF79" s="7"/>
-      <c r="DG79" s="7"/>
-      <c r="DH79" s="7"/>
-      <c r="DI79" s="7"/>
-      <c r="DJ79" s="7"/>
-      <c r="DK79" s="7"/>
-      <c r="DL79" s="7"/>
-      <c r="DM79" s="7"/>
-      <c r="DN79" s="7"/>
-      <c r="DO79" s="7"/>
-      <c r="DP79" s="7"/>
-      <c r="DQ79" s="7"/>
-      <c r="DR79" s="7"/>
-      <c r="DS79" s="7"/>
-      <c r="DT79" s="7"/>
-      <c r="DU79" s="7"/>
-      <c r="DV79" s="7"/>
-      <c r="DW79" s="7"/>
-      <c r="DX79" s="7"/>
-      <c r="DY79" s="7"/>
-      <c r="DZ79" s="7"/>
-      <c r="EA79" s="7"/>
-      <c r="EB79" s="7"/>
-      <c r="EC79" s="7"/>
-      <c r="ED79" s="7"/>
-      <c r="EE79" s="7"/>
-      <c r="EF79" s="7"/>
-      <c r="EG79" s="7"/>
-      <c r="EH79" s="7"/>
-      <c r="EI79" s="7"/>
-      <c r="EJ79" s="7"/>
-      <c r="EK79" s="7"/>
-      <c r="EL79" s="7"/>
-      <c r="EM79" s="7"/>
-      <c r="EN79" s="7"/>
-      <c r="EO79" s="7"/>
-      <c r="EP79" s="7"/>
-      <c r="EQ79" s="7"/>
-      <c r="ER79" s="7"/>
-      <c r="ES79" s="7"/>
-      <c r="ET79" s="7"/>
-      <c r="EU79" s="7"/>
-      <c r="EV79" s="7"/>
-      <c r="EW79" s="7"/>
-      <c r="EX79" s="7"/>
-      <c r="EY79" s="7"/>
-      <c r="EZ79" s="7"/>
-      <c r="FA79" s="7"/>
-      <c r="FB79" s="7"/>
-      <c r="FC79" s="7"/>
-      <c r="FD79" s="7"/>
-      <c r="FE79" s="7"/>
-      <c r="FF79" s="7"/>
-      <c r="FG79" s="7"/>
-      <c r="FH79" s="7"/>
-      <c r="FI79" s="7"/>
-      <c r="FJ79" s="7"/>
-      <c r="FK79" s="7"/>
-      <c r="FL79" s="7"/>
-      <c r="FM79" s="7"/>
-      <c r="FN79" s="7"/>
-      <c r="FO79" s="7"/>
-      <c r="FP79" s="7"/>
-      <c r="FQ79" s="7"/>
-      <c r="FR79" s="7"/>
-      <c r="FS79" s="7"/>
-      <c r="FT79" s="7"/>
-      <c r="FU79" s="7"/>
-      <c r="FV79" s="7"/>
-      <c r="FW79" s="7"/>
-      <c r="FX79" s="7"/>
-      <c r="FY79" s="7"/>
-      <c r="FZ79" s="7"/>
-      <c r="GA79" s="7"/>
-      <c r="GB79" s="7"/>
-      <c r="GC79" s="7"/>
-      <c r="GD79" s="7"/>
-      <c r="GE79" s="7"/>
-      <c r="GF79" s="7"/>
-      <c r="GG79" s="7"/>
-      <c r="GH79" s="7"/>
-      <c r="GI79" s="7"/>
-      <c r="GJ79" s="7"/>
-      <c r="GK79" s="7"/>
-      <c r="GL79" s="7"/>
-      <c r="GM79" s="7"/>
-      <c r="GN79" s="7"/>
-      <c r="GO79" s="7"/>
-      <c r="GP79" s="7"/>
-      <c r="GQ79" s="7"/>
-      <c r="GR79" s="7"/>
-      <c r="GS79" s="7"/>
-      <c r="GT79" s="7"/>
-      <c r="GU79" s="7"/>
-      <c r="GV79" s="7"/>
-      <c r="GW79" s="7"/>
-      <c r="GX79" s="7"/>
-      <c r="GY79" s="7"/>
-      <c r="GZ79" s="7"/>
-      <c r="HA79" s="7"/>
-      <c r="HB79" s="7"/>
-      <c r="HC79" s="7"/>
-      <c r="HD79" s="7"/>
-      <c r="HE79" s="7"/>
-      <c r="HF79" s="7"/>
-      <c r="HG79" s="7"/>
-      <c r="HH79" s="7"/>
-      <c r="HI79" s="7"/>
-      <c r="HJ79" s="7"/>
-      <c r="HK79" s="7"/>
-      <c r="HL79" s="7"/>
-      <c r="HM79" s="7"/>
-      <c r="HN79" s="7"/>
-      <c r="HO79" s="7"/>
-      <c r="HP79" s="7"/>
-      <c r="HQ79" s="7"/>
-      <c r="HR79" s="7"/>
-      <c r="HS79" s="7"/>
-      <c r="HT79" s="7"/>
-      <c r="HU79" s="7"/>
-      <c r="HV79" s="7"/>
-      <c r="HW79" s="7"/>
-      <c r="HX79" s="7"/>
-      <c r="HY79" s="7"/>
-      <c r="HZ79" s="7"/>
-      <c r="IA79" s="7"/>
-      <c r="IB79" s="7"/>
-      <c r="IC79" s="7"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="32"/>
@@ -41853,7 +41819,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" s="7" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="91" t="n">
         <v>47</v>
       </c>
@@ -41958,7 +41924,7 @@
       <c r="BG50" s="91" t="s">
         <v>78</v>
       </c>
-      <c r="BH50" s="0"/>
+      <c r="BH50" s="1"/>
     </row>
     <row r="51" s="7" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="91" t="n">
@@ -42090,7 +42056,7 @@
       <c r="BG51" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="BH51" s="0"/>
+      <c r="BH51" s="1"/>
     </row>
     <row r="52" s="7" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="91" t="n">
@@ -42239,7 +42205,7 @@
       <c r="BG52" s="91" t="s">
         <v>116</v>
       </c>
-      <c r="BH52" s="0"/>
+      <c r="BH52" s="1"/>
     </row>
     <row r="53" s="7" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="91" t="n">
@@ -42388,7 +42354,7 @@
       <c r="BG53" s="91" t="s">
         <v>109</v>
       </c>
-      <c r="BH53" s="0"/>
+      <c r="BH53" s="1"/>
     </row>
     <row r="54" s="7" customFormat="true" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="105"/>
@@ -46582,7 +46548,10 @@
       </c>
       <c r="BD86" s="13"/>
     </row>
-    <row r="87" s="7" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="7"/>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7"/>
       <c r="D87" s="14"/>
       <c r="E87" s="133" t="e">
         <f aca="false">#DIV/0!</f>
@@ -46718,11 +46687,12 @@
         <f aca="false">#DIV/0!</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT87" s="13"/>
+      <c r="AS87" s="7"/>
       <c r="AU87" s="133" t="e">
         <f aca="false">#DIV/0!</f>
         <v>#DIV/0!</v>
       </c>
+      <c r="AV87" s="7"/>
       <c r="AW87" s="133" t="e">
         <f aca="false">#DIV/0!</f>
         <v>#DIV/0!</v>
@@ -46742,13 +46712,20 @@
       <c r="BA87" s="133" t="n">
         <v>0</v>
       </c>
+      <c r="BB87" s="7"/>
       <c r="BC87" s="133" t="e">
         <f aca="false">#DIV/0!</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD87" s="13"/>
-    </row>
-    <row r="88" s="7" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="BE87" s="7"/>
+      <c r="BF87" s="7"/>
+      <c r="BG87" s="7"/>
+      <c r="BH87" s="7"/>
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="7"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="7"/>
       <c r="D88" s="14"/>
       <c r="E88" s="133" t="n">
         <v>0</v>
@@ -46863,10 +46840,11 @@
       <c r="AR88" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="AT88" s="13"/>
+      <c r="AS88" s="7"/>
       <c r="AU88" s="133" t="n">
         <v>0</v>
       </c>
+      <c r="AV88" s="7"/>
       <c r="AW88" s="133" t="n">
         <v>0</v>
       </c>
@@ -46882,10 +46860,14 @@
       <c r="BA88" s="133" t="n">
         <v>2</v>
       </c>
+      <c r="BB88" s="7"/>
       <c r="BC88" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="BD88" s="13"/>
+      <c r="BE88" s="7"/>
+      <c r="BF88" s="7"/>
+      <c r="BG88" s="7"/>
+      <c r="BH88" s="7"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="7"/>
@@ -48143,13 +48125,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L1048576"/>
+  <dimension ref="A1:K1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="17.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="13" width="11.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48162,9 +48143,6 @@
       <c r="C1" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="D1" s="83" t="n">
-        <v>45798.6543402778</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="91" t="s">
@@ -48176,7 +48154,6 @@
       <c r="C2" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="100"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="91" t="s">
@@ -48188,9 +48165,6 @@
       <c r="C3" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="100" t="n">
-        <v>45798.7156365741</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="91" t="s">
@@ -48202,7 +48176,6 @@
       <c r="C4" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D4" s="100"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="91" t="s">
@@ -48214,7 +48187,6 @@
       <c r="C5" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D5" s="100"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="91" t="s">
@@ -48226,9 +48198,6 @@
       <c r="C6" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D6" s="100" t="n">
-        <v>45798.7506712963</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="91" t="s">
@@ -48240,9 +48209,6 @@
       <c r="C7" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D7" s="100" t="n">
-        <v>45798.9043171296</v>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="91" t="s">
@@ -48254,7 +48220,6 @@
       <c r="C8" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="100"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="91" t="s">
@@ -48266,7 +48231,6 @@
       <c r="C9" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D9" s="100"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="91" t="s">
@@ -48278,9 +48242,6 @@
       <c r="C10" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D10" s="100" t="n">
-        <v>45799.0767013889</v>
-      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="91" t="s">
@@ -48292,9 +48253,6 @@
       <c r="C11" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D11" s="100" t="n">
-        <v>45799.5332407407</v>
-      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="91" t="s">
@@ -48306,7 +48264,6 @@
       <c r="C12" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="100"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="91" t="s">
@@ -48318,7 +48275,6 @@
       <c r="C13" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="100"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="91" t="s">
@@ -48330,7 +48286,6 @@
       <c r="C14" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="100"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="91" t="s">
@@ -48342,9 +48297,6 @@
       <c r="C15" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D15" s="100" t="n">
-        <v>45798.8103240741</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="91" t="s">
@@ -48356,9 +48308,6 @@
       <c r="C16" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="100" t="n">
-        <v>45799.1014583333</v>
-      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="91" t="s">
@@ -48370,7 +48319,6 @@
       <c r="C17" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="100"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="91" t="s">
@@ -48382,7 +48330,6 @@
       <c r="C18" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="100"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="91" t="s">
@@ -48394,9 +48341,6 @@
       <c r="C19" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D19" s="100" t="n">
-        <v>45799.8872569444</v>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="91" t="s">
@@ -48408,7 +48352,6 @@
       <c r="C20" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="100"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="91" t="s">
@@ -48420,9 +48363,6 @@
       <c r="C21" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D21" s="100" t="n">
-        <v>45799.3325</v>
-      </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="91" t="s">
@@ -48434,7 +48374,6 @@
       <c r="C22" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D22" s="100"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="91" t="s">
@@ -48446,7 +48385,6 @@
       <c r="C23" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D23" s="100"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="91" t="s">
@@ -48458,9 +48396,6 @@
       <c r="C24" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="100" t="n">
-        <v>45800.0094560185</v>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="91" t="s">
@@ -48472,9 +48407,6 @@
       <c r="C25" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="100" t="n">
-        <v>45798.7045023148</v>
-      </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="91" t="s">
@@ -48486,7 +48418,6 @@
       <c r="C26" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D26" s="100"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="91" t="s">
@@ -48498,7 +48429,6 @@
       <c r="C27" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="100"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="91" t="s">
@@ -48510,9 +48440,6 @@
       <c r="C28" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="100" t="n">
-        <v>45799.6948842593</v>
-      </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="91" t="s">
@@ -48524,7 +48451,6 @@
       <c r="C29" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D29" s="100"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="91" t="s">
@@ -48536,7 +48462,6 @@
       <c r="C30" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="100"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="91" t="s">
@@ -48548,9 +48473,6 @@
       <c r="C31" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="100" t="n">
-        <v>45798.4532523148</v>
-      </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="91" t="s">
@@ -48562,9 +48484,6 @@
       <c r="C32" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D32" s="100" t="n">
-        <v>45799.0405902778</v>
-      </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="91" t="s">
@@ -48576,9 +48495,6 @@
       <c r="C33" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D33" s="100" t="n">
-        <v>45798.2470023148</v>
-      </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="91" t="s">
@@ -48590,9 +48506,6 @@
       <c r="C34" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D34" s="100" t="n">
-        <v>45799.6044212963</v>
-      </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="91" t="s">
@@ -48604,7 +48517,6 @@
       <c r="C35" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="100"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="91" t="s">
@@ -48616,7 +48528,6 @@
       <c r="C36" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D36" s="100"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="91" t="s">
@@ -48628,9 +48539,6 @@
       <c r="C37" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="100" t="n">
-        <v>45799.8260300926</v>
-      </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="91" t="s">
@@ -48642,7 +48550,6 @@
       <c r="C38" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="100"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="91" t="s">
@@ -48654,9 +48561,6 @@
       <c r="C39" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="100" t="n">
-        <v>45798.9312962963</v>
-      </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="91" t="s">
@@ -48668,7 +48572,6 @@
       <c r="C40" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D40" s="100"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="91" t="s">
@@ -48680,7 +48583,6 @@
       <c r="C41" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="100"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="91" t="s">
@@ -48692,9 +48594,6 @@
       <c r="C42" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D42" s="100" t="n">
-        <v>45798.9019675926</v>
-      </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="91" t="s">
@@ -48706,9 +48605,6 @@
       <c r="C43" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="100" t="n">
-        <v>45798.9082060185</v>
-      </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="91" t="s">
@@ -48720,7 +48616,6 @@
       <c r="C44" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="100"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="91" t="s">
@@ -48732,9 +48627,6 @@
       <c r="C45" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D45" s="100" t="n">
-        <v>45798.511724537</v>
-      </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="91" t="s">
@@ -48746,7 +48638,6 @@
       <c r="C46" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="100"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="91" t="s">
@@ -48758,9 +48649,6 @@
       <c r="C47" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D47" s="100" t="n">
-        <v>45798.7746990741</v>
-      </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="91" t="s">
@@ -48772,9 +48660,6 @@
       <c r="C48" s="96" t="n">
         <v>-1</v>
       </c>
-      <c r="D48" s="100" t="n">
-        <v>45799.0463310185</v>
-      </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="91" t="s">
@@ -48786,341 +48671,210 @@
       <c r="C49" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="100" t="n">
-        <v>45798.7252430556</v>
-      </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="106"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="125"/>
-      <c r="D50" s="111"/>
+      <c r="A50" s="7"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="91" t="s">
-        <v>85</v>
-      </c>
-      <c r="B51" s="96" t="s">
-        <v>204</v>
-      </c>
-      <c r="C51" s="96"/>
-      <c r="D51" s="100"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="132"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7"/>
-      <c r="D52" s="127"/>
+      <c r="B52" s="131"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7"/>
-      <c r="B53" s="132"/>
-      <c r="D53" s="132"/>
+      <c r="B53" s="131"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7"/>
-      <c r="B54" s="131"/>
-      <c r="D54" s="131"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7"/>
-      <c r="B55" s="131"/>
-      <c r="D55" s="131"/>
+      <c r="B55" s="135"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7"/>
-      <c r="D56" s="127"/>
+      <c r="B56" s="133"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7"/>
-      <c r="B57" s="135"/>
-      <c r="D57" s="135"/>
+      <c r="B57" s="133"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7"/>
       <c r="B58" s="133"/>
-      <c r="D58" s="133"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7"/>
-      <c r="B59" s="133"/>
-      <c r="D59" s="133"/>
+      <c r="B59" s="136"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7"/>
-      <c r="B60" s="133"/>
-      <c r="D60" s="133"/>
+      <c r="B60" s="135"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7"/>
-      <c r="B61" s="136"/>
-      <c r="D61" s="136"/>
+      <c r="B61" s="133"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7"/>
-      <c r="B62" s="135"/>
-      <c r="D62" s="135"/>
+      <c r="B62" s="133"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
       <c r="B63" s="133"/>
-      <c r="D63" s="133"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
-      <c r="B64" s="133"/>
-      <c r="D64" s="133"/>
+      <c r="B64" s="136"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
-      <c r="B65" s="133"/>
-      <c r="D65" s="133"/>
+      <c r="B65" s="135"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7"/>
-      <c r="B66" s="136"/>
-      <c r="D66" s="136"/>
+      <c r="B66" s="133"/>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
-      <c r="B67" s="135"/>
-      <c r="D67" s="135"/>
+      <c r="B67" s="133"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7"/>
       <c r="B68" s="133"/>
-      <c r="D68" s="133"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7"/>
-      <c r="B69" s="133"/>
-      <c r="D69" s="133"/>
+      <c r="B69" s="136"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7"/>
-      <c r="B70" s="133"/>
-      <c r="D70" s="133"/>
+      <c r="B70" s="135"/>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7"/>
-      <c r="B71" s="136"/>
-      <c r="D71" s="136"/>
+      <c r="B71" s="133"/>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7"/>
-      <c r="B72" s="135"/>
-      <c r="D72" s="135"/>
+      <c r="B72" s="133"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7"/>
       <c r="B73" s="133"/>
-      <c r="D73" s="133"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7"/>
-      <c r="B74" s="133"/>
-      <c r="D74" s="133"/>
+      <c r="B74" s="136"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7"/>
-      <c r="B75" s="133"/>
-      <c r="D75" s="133"/>
+      <c r="B75" s="135"/>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7"/>
-      <c r="B76" s="136"/>
-      <c r="D76" s="136"/>
+      <c r="B76" s="133"/>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7"/>
-      <c r="B77" s="135"/>
-      <c r="D77" s="135"/>
+      <c r="B77" s="133"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7"/>
       <c r="B78" s="133"/>
-      <c r="D78" s="133"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7"/>
-      <c r="B79" s="133"/>
-      <c r="D79" s="133"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7"/>
-      <c r="B80" s="133"/>
-      <c r="D80" s="133"/>
+      <c r="B80" s="135"/>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7"/>
-      <c r="D81" s="7"/>
+      <c r="B81" s="133"/>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7"/>
-      <c r="B82" s="135"/>
-      <c r="D82" s="135"/>
+      <c r="B82" s="133"/>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7"/>
       <c r="B83" s="133"/>
-      <c r="D83" s="133"/>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7"/>
-      <c r="B84" s="133"/>
-      <c r="D84" s="133"/>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7"/>
-      <c r="B85" s="133"/>
-      <c r="D85" s="133"/>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7"/>
-      <c r="D86" s="127"/>
-    </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7"/>
-      <c r="D87" s="127"/>
+    </row>
+    <row r="87" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C87" s="138"/>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7"/>
-      <c r="D88" s="127"/>
-    </row>
-    <row r="89" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C89" s="138"/>
-      <c r="D89" s="137"/>
+      <c r="C88" s="139"/>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C89" s="140"/>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C90" s="139"/>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C91" s="140"/>
-      <c r="D91" s="7"/>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C92" s="139"/>
-      <c r="D92" s="7"/>
-    </row>
-    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C93" s="140"/>
-      <c r="D93" s="7"/>
-    </row>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C94" s="139"/>
-      <c r="D94" s="7"/>
-    </row>
-    <row r="95" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D95" s="137"/>
-    </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D97" s="7"/>
-    </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D98" s="7"/>
-    </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D99" s="7"/>
-    </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D100" s="7"/>
-    </row>
-    <row r="101" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D101" s="137"/>
-    </row>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D103" s="7"/>
-    </row>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D104" s="7"/>
-    </row>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D105" s="7"/>
-    </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D106" s="7"/>
-    </row>
-    <row r="107" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D107" s="137"/>
-    </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D109" s="7"/>
-    </row>
-    <row r="110" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D110" s="7"/>
-      <c r="E110" s="145"/>
-      <c r="F110" s="145"/>
-      <c r="G110" s="145"/>
-      <c r="H110" s="145"/>
-      <c r="I110" s="145"/>
-      <c r="J110" s="145"/>
-      <c r="K110" s="145"/>
-      <c r="L110" s="145"/>
-    </row>
-    <row r="111" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D111" s="7"/>
-      <c r="E111" s="146"/>
-      <c r="F111" s="146"/>
-      <c r="G111" s="146"/>
-      <c r="H111" s="146"/>
-      <c r="I111" s="146"/>
-      <c r="J111" s="146"/>
-      <c r="K111" s="146"/>
-      <c r="L111" s="146"/>
-    </row>
-    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D112" s="7"/>
-    </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D113" s="7"/>
-    </row>
-    <row r="114" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D114" s="145"/>
-      <c r="E114" s="145"/>
-      <c r="F114" s="145"/>
-      <c r="G114" s="145"/>
-      <c r="H114" s="145"/>
-      <c r="I114" s="145"/>
-      <c r="J114" s="145"/>
-      <c r="K114" s="145"/>
-      <c r="L114" s="145"/>
-    </row>
-    <row r="115" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D115" s="146"/>
-      <c r="E115" s="146"/>
-      <c r="F115" s="146"/>
-      <c r="G115" s="146"/>
-      <c r="H115" s="146"/>
-      <c r="I115" s="146"/>
-      <c r="J115" s="146"/>
-      <c r="K115" s="146"/>
-      <c r="L115" s="146"/>
-    </row>
-    <row r="116" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D116" s="137"/>
-    </row>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D117" s="7"/>
-    </row>
-    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D118" s="7"/>
-    </row>
-    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D119" s="7"/>
-    </row>
-    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D120" s="7"/>
-    </row>
-    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D121" s="7"/>
-    </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="108" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D108" s="145"/>
+      <c r="E108" s="145"/>
+      <c r="F108" s="145"/>
+      <c r="G108" s="145"/>
+      <c r="H108" s="145"/>
+      <c r="I108" s="145"/>
+      <c r="J108" s="145"/>
+      <c r="K108" s="145"/>
+    </row>
+    <row r="109" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D109" s="146"/>
+      <c r="E109" s="146"/>
+      <c r="F109" s="146"/>
+      <c r="G109" s="146"/>
+      <c r="H109" s="146"/>
+      <c r="I109" s="146"/>
+      <c r="J109" s="146"/>
+      <c r="K109" s="146"/>
+    </row>
+    <row r="112" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D112" s="145"/>
+      <c r="E112" s="145"/>
+      <c r="F112" s="145"/>
+      <c r="G112" s="145"/>
+      <c r="H112" s="145"/>
+      <c r="I112" s="145"/>
+      <c r="J112" s="145"/>
+      <c r="K112" s="145"/>
+    </row>
+    <row r="113" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D113" s="146"/>
+      <c r="E113" s="146"/>
+      <c r="F113" s="146"/>
+      <c r="G113" s="146"/>
+      <c r="H113" s="146"/>
+      <c r="I113" s="146"/>
+      <c r="J113" s="146"/>
+      <c r="K113" s="146"/>
+    </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D114:L114"/>
-    <mergeCell ref="D115:L115"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -49128,6 +48882,5 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>